--- a/outputs/marine_equipment/Логистика_варианты.xlsx
+++ b/outputs/marine_equipment/Логистика_варианты.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>во Владивостоке и столько же в Петербурге</t>
+          <t>во Владивостоке и столько же в Петербурге — подтверждено</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>во Владивостоке и столько же в Петербурге</t>
+          <t>во Владивостоке, в Петербурге принята по аналогии — уточнить</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Ставка на машину в Петербурге принята такой же, как во Владивостоке. Как узнаете настоящую — поправьте, считать заново не придется.</t>
+          <t>По двадцатифутовому ставка в Петербурге подтверждена: 27 тысяч, как и во Владивостоке. По сорокафутовому принята по аналогии, 37 тысяч — уточнить. Все ставки в желтых ячейках.</t>
         </is>
       </c>
     </row>

--- a/outputs/marine_equipment/Логистика_варианты.xlsx
+++ b/outputs/marine_equipment/Логистика_варианты.xlsx
@@ -504,18 +504,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -624,444 +626,401 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Доска сырая, кг в кубометре</t>
+          <t>Подача погрузчика, за выезд</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>платится один раз за день погрузки</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>Погрузчик, руб за час</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Грузчики, человек</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Грузчик, руб за час</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>750</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>бригада обходится в 3 000 руб в час</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Часов на контейнер</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>погрузка контейнера — 32 000 руб</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Доска сырая, кг в кубометре</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>Доски на тонну груза, куб. м</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B17" s="6" t="n">
         <v>0.035</v>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>43,4 кв. м настилов на 27,3 т арматуры</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>По двадцатифутовому ставка в Петербурге подтверждена: 27 тысяч, как и во Владивостоке. По сорокафутовому принята по аналогии, 37 тысяч — уточнить. Все ставки в желтых ячейках.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Варианты</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Контейнеры</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Увезет, т</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Останется, т</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>Доска, кг</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>Контейнеры и авто, руб</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Погрузка, руб</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Остаток через ТК, руб</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>Погрузка остатка, руб</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>ВСЕГО за всю арматуру, руб</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>Руб за увезенную тонну</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Один сорокафутовый</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C23" s="10" t="n">
         <v>25.35410994327091</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D23" s="10" t="n">
         <v>1.944473236317666</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E23" s="11" t="n">
         <v>621</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F23" s="11" t="n">
         <v>509000</v>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="G23" s="11" t="n">
+        <v>32000</v>
+      </c>
+      <c r="H23" s="11" t="n">
         <v>157502.332141731</v>
       </c>
-      <c r="H18" s="12" t="n">
-        <v>666502.3321417309</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <v>20075.64064125591</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="I23" s="11" t="n">
+        <v>22000</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>720502.3321417309</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>21337.76343206178</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Два двадцатифутовых по 22 т</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n">
+      <c r="B24" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C24" s="14" t="n">
         <v>27.29858317958857</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D24" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="15" t="n">
+      <c r="E24" s="15" t="n">
         <v>1043</v>
       </c>
-      <c r="F19" s="15" t="n">
+      <c r="F24" s="15" t="n">
         <v>580000</v>
       </c>
-      <c r="G19" s="15" t="n">
+      <c r="G24" s="15" t="n">
+        <v>52000</v>
+      </c>
+      <c r="H24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="15" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v>21246.52390141888</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="I24" s="15" t="n"/>
+      <c r="J24" s="15" t="n">
+        <v>632000</v>
+      </c>
+      <c r="K24" s="15" t="n">
+        <v>23151.38466499437</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Один двадцатифутовый 22 т</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="10" t="n">
+      <c r="C25" s="10" t="n">
         <v>21.28126179181153</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D25" s="10" t="n">
         <v>6.017321387777036</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E25" s="11" t="n">
         <v>521</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F25" s="11" t="n">
         <v>290000</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G25" s="11" t="n">
+        <v>32000</v>
+      </c>
+      <c r="H25" s="11" t="n">
         <v>487403.0324099399</v>
       </c>
-      <c r="H20" s="12" t="n">
-        <v>777403.0324099399</v>
-      </c>
-      <c r="I20" s="11" t="n">
-        <v>13627.01153892972</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Один усиленный двадцатифутовый</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="10" t="n">
-        <v>21.03959718437781</v>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>6.258985995210762</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>515</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>369000</v>
-      </c>
-      <c r="G21" s="11" t="n">
-        <v>506977.8656120717</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>875977.8656120717</v>
-      </c>
-      <c r="I21" s="11" t="n">
-        <v>17538.35858958305</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>Сорокафутовый и двадцатифутовый</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" s="10" t="n">
-        <v>27.29858317958857</v>
-      </c>
-      <c r="D22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>1143</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>799000</v>
-      </c>
-      <c r="G22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>799000</v>
-      </c>
-      <c r="I22" s="11" t="n">
-        <v>29268.91827109256</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Что в каждом контейнере</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Контейнер</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Груз, т</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Доска, кг</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>Объем, куб. м</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Позиций</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>Контейнер, руб</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Авто туда и обратно, руб</t>
-        </is>
+      <c r="I25" s="11" t="n">
+        <v>22000</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>831403.0324099399</v>
+      </c>
+      <c r="K25" s="11" t="n">
+        <v>15130.68177770817</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Один сорокафутовый</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>40 футов</t>
-        </is>
+          <t>Один усиленный двадцатифутовый</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>25.35410994327091</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>621</v>
+        <v>21.03959718437781</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>6.258985995210762</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>283</v>
+        <v>515</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>369000</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>435000</v>
+        <v>32000</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>74000</v>
+        <v>506977.8656120717</v>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>22000</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>929977.8656120717</v>
+      </c>
+      <c r="K26" s="11" t="n">
+        <v>19059.30025588836</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Два двадцатифутовых по 22 т</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>20 футов</t>
-        </is>
+          <t>Сорокафутовый и двадцатифутовый</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>21.28126179181153</v>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>521</v>
+        <v>27.29858317958857</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>233</v>
+        <v>1143</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>799000</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>236000</v>
+        <v>64000</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>54000</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr"/>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>20 футов</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="n">
-        <v>21.28126179181153</v>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>521</v>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>233</v>
-      </c>
-      <c r="G28" s="11" t="n">
-        <v>236000</v>
-      </c>
-      <c r="H28" s="11" t="n">
-        <v>54000</v>
+        <v>0</v>
+      </c>
+      <c r="I27" s="11" t="n"/>
+      <c r="J27" s="12" t="n">
+        <v>863000</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>31613.36228780085</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Один двадцатифутовый 22 т</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>20 футов</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>21.28126179181153</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>521</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>233</v>
-      </c>
-      <c r="G29" s="11" t="n">
-        <v>236000</v>
-      </c>
-      <c r="H29" s="11" t="n">
-        <v>54000</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>Один усиленный двадцатифутовый</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>20 футов</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="n">
-        <v>21.03959718437781</v>
-      </c>
-      <c r="D30" s="11" t="n">
-        <v>515</v>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>232</v>
-      </c>
-      <c r="G30" s="11" t="n">
-        <v>315000</v>
-      </c>
-      <c r="H30" s="11" t="n">
-        <v>54000</v>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Что в каждом контейнере</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Контейнер</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Груз, т</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Доска, кг</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Объем, куб. м</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Позиций</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>Контейнер, руб</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>Авто туда и обратно, руб</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Сорокафутовый и двадцатифутовый</t>
+          <t>Один сорокафутовый</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1089,7 +1048,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr"/>
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Два двадцатифутовых по 22 т</t>
+        </is>
+      </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
           <t>20 футов</t>
@@ -1114,52 +1077,222 @@
         <v>54000</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr"/>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>20 футов</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="n">
+        <v>21.28126179181153</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>521</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>233</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>236000</v>
+      </c>
+      <c r="H33" s="11" t="n">
+        <v>54000</v>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Один двадцатифутовый 22 т</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>20 футов</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="n">
+        <v>21.28126179181153</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>521</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>233</v>
+      </c>
+      <c r="G34" s="11" t="n">
+        <v>236000</v>
+      </c>
+      <c r="H34" s="11" t="n">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Один усиленный двадцатифутовый</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>20 футов</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="n">
+        <v>21.03959718437781</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>515</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>232</v>
+      </c>
+      <c r="G35" s="11" t="n">
+        <v>315000</v>
+      </c>
+      <c r="H35" s="11" t="n">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Сорокафутовый и двадцатифутовый</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>40 футов</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v>25.35410994327091</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>621</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="G36" s="11" t="n">
+        <v>435000</v>
+      </c>
+      <c r="H36" s="11" t="n">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr"/>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>20 футов</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>21.28126179181153</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>521</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>233</v>
+      </c>
+      <c r="G37" s="11" t="n">
+        <v>236000</v>
+      </c>
+      <c r="H37" s="11" t="n">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Выводы</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>— Чтобы увезти всю арматуру  дешевле всего «Два двадцатифутовых по 22 т»: 580 000 руб против 875 978 у худшего варианта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>— Два двадцатифутовых дороже сорокафутового по расходам на 71 000 руб  но увозят на 1.94 т больше и не оставляют ничего. Через транспортную компанию эти тонны стоили бы 157 502 руб.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>— Один двадцатифутовый самый дешевый по ставке — 290 000 руб  и самая низкая цена тонны 13 627. Но он оставляет 6.02 т  и если их везти транспортной компанией  вариант становится худшим: 777 403 руб.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>— Усиленный двадцатифутовый бессмыслен при любом раскладе: он того же размера, что обычный, объем кончается на тех же тоннах, а стоит на 79 тысяч дороже.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>— Доска съедает 621 кг в сорокафутовом и по 521 кг в каждом двадцатифутовом. Это не мелочь: в двадцатифутовом полтонны доски это полтонны неувезенной арматуры.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="16" t="inlineStr">
         <is>
+          <t>— Чтобы увезти всю арматуру  дешевле всего «Два двадцатифутовых по 22 т»: 632 000 руб против 929 978 у худшего варианта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>— Два двадцатифутовых дороже сорокафутового по расходам на 71 000 руб  но увозят на 1.94 т больше и не оставляют ничего. Через транспортную компанию эти тонны стоили бы 157 502 руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>— Один двадцатифутовый самый дешевый по ставке — 290 000 руб  и самая низкая цена тонны 15 131. Но он оставляет 6.02 т  и если их везти транспортной компанией  вариант становится худшим: 831 403 руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>— Усиленный двадцатифутовый бессмыслен при любом раскладе: он того же размера, что обычный, объем кончается на тех же тоннах, а стоит на 79 тысяч дороже.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>— Доска съедает 621 кг в сорокафутовом и по 521 кг в каждом двадцатифутовом. Это не мелочь: в двадцатифутовом полтонны доски это полтонны неувезенной арматуры.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
           <t>— Автодоставка добавляет 54 тысячи на двадцатифутовый и 74 на сорокафутовый, считая оба конца. На двух контейнерах это 108 тысяч — больше, чем разница в ставке за сами контейнеры.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>— Погрузка на двух двадцатифутовых стоит 52 000 руб против 32 000 на сорокафутовом. Разница всего 20 000 руб  и только потому  что оба контейнера грузим в один день и подачу погрузчика платим один раз. Разными днями это 64 000 руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>— У сорокафутового погрузка не заканчивается контейнером: 1.94 т остатка надо грузить отдельным днем  это еще одна подача погрузчика и бригада — 22 000 руб сверх тарифа ТК.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>— Выгрузка в Петербурге в расчет не входит: ставок на тамошний погрузчик и грузчиков у нас нет. По владивостокским это около 32 000 руб на контейнер  и считать надо отдельно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>— Сохранность груза тоже за два двадцатифутовых: при равной развеске в каждом едет около 13,7 т вместо 25, пирог ниже, на нижние задвижки давит вдвое меньше, и мелочь не оказывается под тяжелым. Разбивку считает build_two_containers.py.</t>
         </is>
       </c>
     </row>

--- a/outputs/marine_equipment/Логистика_варианты.xlsx
+++ b/outputs/marine_equipment/Логистика_варианты.xlsx
@@ -80,12 +80,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDF2E3"/>
+        <fgColor rgb="00EAF3EA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF3EA"/>
+        <fgColor rgb="00FDF2E3"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,13 +129,15 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -504,20 +506,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Вся арматура — 27.30 т. Считаем полные расходы: контейнер, автодоставка во Владивостоке и автодоставка в Петербурге. Вес сырой необрезной доски входит в лимит контейнера.</t>
+          <t>Весь перечень — 27.30 т и 38.7 куб. м, это 706 кг на кубометр. Расходы считаем полностью: контейнер, авто на обоих концах, погрузка, доска и остаток через транспортную компанию.</t>
         </is>
       </c>
     </row>
@@ -563,7 +567,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>грузоподъемность не работает: объем кончается раньше</t>
+          <t>27 тонн паспортных, но внутри те же 33 куб. м</t>
         </is>
       </c>
     </row>
@@ -712,25 +716,25 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>43,4 кв. м настилов на 27,3 т арматуры</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>По двадцатифутовому ставка в Петербурге подтверждена: 27 тысяч, как и во Владивостоке. По сорокафутовому принята по аналогии, 37 тысяч — уточнить. Все ставки в желтых ячейках.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Варианты</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="34" customHeight="1">
+          <t>25 кг доски на каждую тонну арматуры</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>По очередности покупателя</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Сначала согласованный список менеджера целиком, потом добор со склада по цене за килограмм. Так и будем грузить.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Вариант</t>
@@ -738,50 +742,60 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Контейнеры</t>
+          <t>Корпусов</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Увезет, т</t>
+          <t>Увезет груза, т</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
+          <t>Доска, кг</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Брутто, т</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Во что уперся</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
           <t>Останется, т</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>Доска, кг</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Контейнеры и авто, руб</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>Погрузка, руб</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>Остаток через ТК, руб</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>Погрузка остатка, руб</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>ВСЕГО за всю арматуру, руб</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="inlineStr">
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>ВСЕГО, руб</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
         <is>
           <t>Руб за увезенную тонну</t>
         </is>
@@ -790,347 +804,389 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
+          <t>Два двадцатифутовых по 22 т</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>27.29858317958968</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>669</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>27.96739846748962</v>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>груз кончился, объем</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="11" t="n">
+        <v>580000</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>52000</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="11" t="n"/>
+      <c r="L23" s="11" t="n">
+        <v>632000</v>
+      </c>
+      <c r="M23" s="11" t="n">
+        <v>23151.38466499343</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Один усиленный двадцатифутовый</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>21.0817771442884</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>517</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>21.59828068432347</v>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>объем</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>6.216806035301273</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>369000</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>32000</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>503561.2888594032</v>
+      </c>
+      <c r="K24" s="14" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L24" s="15" t="n">
+        <v>926561.2888594032</v>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>19021.16682362527</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
           <t>Один сорокафутовый</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
+      <c r="B25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="10" t="n">
-        <v>25.35410994327091</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>1.944473236317666</v>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>621</v>
-      </c>
-      <c r="F23" s="11" t="n">
+      <c r="C25" s="13" t="n">
+        <v>25.3741099432722</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>622</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>25.99577563688237</v>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>вес</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>1.924473236317662</v>
+      </c>
+      <c r="H25" s="14" t="n">
         <v>509000</v>
       </c>
-      <c r="G23" s="11" t="n">
+      <c r="I25" s="14" t="n">
         <v>32000</v>
       </c>
-      <c r="H23" s="11" t="n">
-        <v>157502.332141731</v>
-      </c>
-      <c r="I23" s="11" t="n">
+      <c r="J25" s="14" t="n">
+        <v>155882.3321417306</v>
+      </c>
+      <c r="K25" s="14" t="n">
         <v>22000</v>
       </c>
-      <c r="J23" s="12" t="n">
-        <v>720502.3321417309</v>
-      </c>
-      <c r="K23" s="11" t="n">
-        <v>21337.76343206178</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="L25" s="15" t="n">
+        <v>718882.3321417306</v>
+      </c>
+      <c r="M25" s="14" t="n">
+        <v>21320.94490051041</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Один двадцатифутовый 22 т</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>21.0817771442884</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>517</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>21.59828068432347</v>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>объем</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>6.216806035301273</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>290000</v>
+      </c>
+      <c r="I26" s="14" t="n">
+        <v>32000</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>503561.2888594032</v>
+      </c>
+      <c r="K26" s="14" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L26" s="15" t="n">
+        <v>847561.2888594032</v>
+      </c>
+      <c r="M26" s="14" t="n">
+        <v>15273.8546563774</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Усиленный и обычный двадцатифутовые</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>27.29858317958968</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>669</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>27.96739846748962</v>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>груз кончился, объем</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>659000</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>64000</v>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="14" t="n"/>
+      <c r="L27" s="15" t="n">
+        <v>723000</v>
+      </c>
+      <c r="M27" s="14" t="n">
+        <v>26484.89100125039</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Сорокафутовый и двадцатифутовый</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>27.29858317958986</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>669</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>27.96739846748982</v>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>вес, груз кончился</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>799000</v>
+      </c>
+      <c r="I28" s="14" t="n">
+        <v>64000</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="14" t="n"/>
+      <c r="L28" s="15" t="n">
+        <v>863000</v>
+      </c>
+      <c r="M28" s="14" t="n">
+        <v>31613.36228779936</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Самое плотное вперед</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Теоретический максимум тонн в корпус. Так грузить нельзя: плотное — это мелочь в ящиках, а крупные клинкеты, которые покупатель просил первыми, самые объемные и уехали бы последними.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="44" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Корпусов</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Увезет груза, т</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Доска, кг</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Брутто, т</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Во что уперся</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>Останется, т</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Контейнеры и авто, руб</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>Погрузка, руб</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>Остаток через ТК, руб</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>Погрузка остатка, руб</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>ВСЕГО, руб</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>Руб за увезенную тонну</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>Два двадцатифутовых по 22 т</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n">
+      <c r="B34" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="14" t="n">
-        <v>27.29858317958857</v>
-      </c>
-      <c r="D24" s="14" t="n">
+      <c r="C34" s="13" t="n">
+        <v>27.29858317958847</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>669</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>27.96739846748839</v>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>вес, груз кончился</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="15" t="n">
-        <v>1043</v>
-      </c>
-      <c r="F24" s="15" t="n">
+      <c r="H34" s="14" t="n">
         <v>580000</v>
       </c>
-      <c r="G24" s="15" t="n">
+      <c r="I34" s="14" t="n">
         <v>52000</v>
       </c>
-      <c r="H24" s="15" t="n">
+      <c r="J34" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="15" t="n">
+      <c r="K34" s="14" t="n"/>
+      <c r="L34" s="15" t="n">
         <v>632000</v>
       </c>
-      <c r="K24" s="15" t="n">
-        <v>23151.38466499437</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Один двадцатифутовый 22 т</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="10" t="n">
-        <v>21.28126179181153</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>6.017321387777036</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>521</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>290000</v>
-      </c>
-      <c r="G25" s="11" t="n">
-        <v>32000</v>
-      </c>
-      <c r="H25" s="11" t="n">
-        <v>487403.0324099399</v>
-      </c>
-      <c r="I25" s="11" t="n">
-        <v>22000</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>831403.0324099399</v>
-      </c>
-      <c r="K25" s="11" t="n">
-        <v>15130.68177770817</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>Один усиленный двадцатифутовый</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="10" t="n">
-        <v>21.03959718437781</v>
-      </c>
-      <c r="D26" s="10" t="n">
-        <v>6.258985995210762</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>515</v>
-      </c>
-      <c r="F26" s="11" t="n">
-        <v>369000</v>
-      </c>
-      <c r="G26" s="11" t="n">
-        <v>32000</v>
-      </c>
-      <c r="H26" s="11" t="n">
-        <v>506977.8656120717</v>
-      </c>
-      <c r="I26" s="11" t="n">
-        <v>22000</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>929977.8656120717</v>
-      </c>
-      <c r="K26" s="11" t="n">
-        <v>19059.30025588836</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>Сорокафутовый и двадцатифутовый</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C27" s="10" t="n">
-        <v>27.29858317958857</v>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>1143</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>799000</v>
-      </c>
-      <c r="G27" s="11" t="n">
-        <v>64000</v>
-      </c>
-      <c r="H27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="11" t="n"/>
-      <c r="J27" s="12" t="n">
-        <v>863000</v>
-      </c>
-      <c r="K27" s="11" t="n">
-        <v>31613.36228780085</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Что в каждом контейнере</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Контейнер</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Груз, т</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Доска, кг</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>Объем, куб. м</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>Позиций</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>Контейнер, руб</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>Авто туда и обратно, руб</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>Один сорокафутовый</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>40 футов</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="n">
-        <v>25.35410994327091</v>
-      </c>
-      <c r="D31" s="11" t="n">
-        <v>621</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>283</v>
-      </c>
-      <c r="G31" s="11" t="n">
-        <v>435000</v>
-      </c>
-      <c r="H31" s="11" t="n">
-        <v>74000</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>Два двадцатифутовых по 22 т</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>20 футов</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="n">
-        <v>21.28126179181153</v>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>521</v>
-      </c>
-      <c r="E32" s="11" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="F32" s="9" t="n">
-        <v>233</v>
-      </c>
-      <c r="G32" s="11" t="n">
-        <v>236000</v>
-      </c>
-      <c r="H32" s="11" t="n">
-        <v>54000</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr"/>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>20 футов</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="n">
-        <v>21.28126179181153</v>
-      </c>
-      <c r="D33" s="11" t="n">
-        <v>521</v>
-      </c>
-      <c r="E33" s="11" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>233</v>
-      </c>
-      <c r="G33" s="11" t="n">
-        <v>236000</v>
-      </c>
-      <c r="H33" s="11" t="n">
-        <v>54000</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>Один двадцатифутовый 22 т</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>20 футов</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="n">
-        <v>21.28126179181153</v>
-      </c>
-      <c r="D34" s="11" t="n">
-        <v>521</v>
-      </c>
-      <c r="E34" s="11" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="F34" s="9" t="n">
-        <v>233</v>
-      </c>
-      <c r="G34" s="11" t="n">
-        <v>236000</v>
-      </c>
-      <c r="H34" s="11" t="n">
-        <v>54000</v>
+      <c r="M34" s="14" t="n">
+        <v>23151.38466499445</v>
       </c>
     </row>
     <row r="35">
@@ -1139,160 +1195,755 @@
           <t>Один усиленный двадцатифутовый</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>20 футов</t>
-        </is>
+      <c r="B35" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="C35" s="10" t="n">
-        <v>21.03959718437781</v>
+        <v>25.20501317784694</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>515</v>
-      </c>
-      <c r="E35" s="11" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="F35" s="9" t="n">
-        <v>232</v>
-      </c>
-      <c r="G35" s="11" t="n">
-        <v>315000</v>
+        <v>618</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>25.82253600070419</v>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>объем</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>2.093570001741579</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>54000</v>
+        <v>369000</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>32000</v>
+      </c>
+      <c r="J35" s="11" t="n">
+        <v>169579.1701410679</v>
+      </c>
+      <c r="K35" s="11" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L35" s="11" t="n">
+        <v>592579.1701410678</v>
+      </c>
+      <c r="M35" s="11" t="n">
+        <v>15909.53343965894</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Один сорокафутовый</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="13" t="n">
+        <v>25.37798218937958</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>622</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>25.99974275301938</v>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>вес</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>1.920600990208946</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>509000</v>
+      </c>
+      <c r="I36" s="14" t="n">
+        <v>32000</v>
+      </c>
+      <c r="J36" s="14" t="n">
+        <v>155568.6802069246</v>
+      </c>
+      <c r="K36" s="14" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L36" s="15" t="n">
+        <v>718568.6802069247</v>
+      </c>
+      <c r="M36" s="14" t="n">
+        <v>21317.69168891619</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Один двадцатифутовый 22 т</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>21.47385505985811</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>526</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>21.99996450882463</v>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>вес</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>5.824728119730372</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>290000</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>32000</v>
+      </c>
+      <c r="J37" s="14" t="n">
+        <v>471802.9776981601</v>
+      </c>
+      <c r="K37" s="14" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L37" s="15" t="n">
+        <v>815802.9776981601</v>
+      </c>
+      <c r="M37" s="14" t="n">
+        <v>14994.97873588273</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Усиленный и обычный двадцатифутовые</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>27.29858317958852</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>669</v>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>27.96739846748843</v>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>груз кончился, объем</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>659000</v>
+      </c>
+      <c r="I38" s="14" t="n">
+        <v>64000</v>
+      </c>
+      <c r="J38" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="14" t="n"/>
+      <c r="L38" s="15" t="n">
+        <v>723000</v>
+      </c>
+      <c r="M38" s="14" t="n">
+        <v>26484.89100125152</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>Сорокафутовый и двадцатифутовый</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>40 футов</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="n">
-        <v>25.35410994327091</v>
-      </c>
-      <c r="D36" s="11" t="n">
-        <v>621</v>
-      </c>
-      <c r="E36" s="11" t="n">
+      <c r="B39" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>27.29858317958853</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>669</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>27.96739846748845</v>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>вес, груз кончился</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>799000</v>
+      </c>
+      <c r="I39" s="14" t="n">
+        <v>64000</v>
+      </c>
+      <c r="J39" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="14" t="n"/>
+      <c r="L39" s="15" t="n">
+        <v>863000</v>
+      </c>
+      <c r="M39" s="14" t="n">
+        <v>31613.3622878009</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Что в каждом корпусе — по очередности покупателя</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Корпус</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Груз, т</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Доска, кг</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Брутто, т</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Из лимита</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>Объем груза, куб. м</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>Доска, куб. м</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>Объем занят</t>
+        </is>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>Во что уперся</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>Позиций</t>
+        </is>
+      </c>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t>Штук</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Два двадцатифутовых по 22 т</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>20 футов, 22 т</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="n">
+        <v>21.0817771442884</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>517</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>21.59828068432347</v>
+      </c>
+      <c r="F43" s="16" t="n">
+        <v>0.981740031105612</v>
+      </c>
+      <c r="G43" s="14" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="H43" s="13" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I43" s="16" t="n">
+        <v>0.9999806727288048</v>
+      </c>
+      <c r="J43" s="12" t="inlineStr">
+        <is>
+          <t>объем</t>
+        </is>
+      </c>
+      <c r="K43" s="14" t="n">
+        <v>213</v>
+      </c>
+      <c r="L43" s="14" t="n">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr"/>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>20 футов, 22 т</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="n">
+        <v>6.216806035301278</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>152</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>6.369117783166159</v>
+      </c>
+      <c r="F44" s="17" t="n">
+        <v>0.28950535378028</v>
+      </c>
+      <c r="G44" s="14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H44" s="13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I44" s="17" t="n">
+        <v>0.2011390367041068</v>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>груз кончился</t>
+        </is>
+      </c>
+      <c r="K44" s="14" t="n">
+        <v>76</v>
+      </c>
+      <c r="L44" s="14" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Один усиленный двадцатифутовый</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>20 футов усиленный, 27 т</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="n">
+        <v>21.0817771442884</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>517</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>21.59828068432347</v>
+      </c>
+      <c r="F45" s="17" t="n">
+        <v>0.7999363216416098</v>
+      </c>
+      <c r="G45" s="14" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="H45" s="13" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I45" s="16" t="n">
+        <v>0.9999806727288048</v>
+      </c>
+      <c r="J45" s="12" t="inlineStr">
+        <is>
+          <t>объем</t>
+        </is>
+      </c>
+      <c r="K45" s="14" t="n">
+        <v>213</v>
+      </c>
+      <c r="L45" s="14" t="n">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>Один сорокафутовый</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>40 футов, 26 т</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="n">
+        <v>25.3741099432722</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>622</v>
+      </c>
+      <c r="E46" s="13" t="n">
+        <v>25.99577563688237</v>
+      </c>
+      <c r="F46" s="16" t="n">
+        <v>0.9998375244954757</v>
+      </c>
+      <c r="G46" s="14" t="n">
         <v>37.4</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="H46" s="13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I46" s="17" t="n">
+        <v>0.5703957417859358</v>
+      </c>
+      <c r="J46" s="12" t="inlineStr">
+        <is>
+          <t>вес</t>
+        </is>
+      </c>
+      <c r="K46" s="14" t="n">
         <v>283</v>
       </c>
-      <c r="G36" s="11" t="n">
-        <v>435000</v>
-      </c>
-      <c r="H36" s="11" t="n">
-        <v>74000</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr"/>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>20 футов</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="n">
-        <v>21.28126179181153</v>
-      </c>
-      <c r="D37" s="11" t="n">
-        <v>521</v>
-      </c>
-      <c r="E37" s="11" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>233</v>
-      </c>
-      <c r="G37" s="11" t="n">
-        <v>236000</v>
-      </c>
-      <c r="H37" s="11" t="n">
-        <v>54000</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="L46" s="14" t="n">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Один двадцатифутовый 22 т</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>20 футов, 22 т</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="n">
+        <v>21.0817771442884</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>517</v>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>21.59828068432347</v>
+      </c>
+      <c r="F47" s="16" t="n">
+        <v>0.981740031105612</v>
+      </c>
+      <c r="G47" s="14" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="H47" s="13" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I47" s="16" t="n">
+        <v>0.9999806727288048</v>
+      </c>
+      <c r="J47" s="12" t="inlineStr">
+        <is>
+          <t>объем</t>
+        </is>
+      </c>
+      <c r="K47" s="14" t="n">
+        <v>213</v>
+      </c>
+      <c r="L47" s="14" t="n">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Усиленный и обычный двадцатифутовые</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>20 футов усиленный, 27 т</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="n">
+        <v>21.0817771442884</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>517</v>
+      </c>
+      <c r="E48" s="13" t="n">
+        <v>21.59828068432347</v>
+      </c>
+      <c r="F48" s="17" t="n">
+        <v>0.7999363216416098</v>
+      </c>
+      <c r="G48" s="14" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="H48" s="13" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I48" s="16" t="n">
+        <v>0.9999806727288048</v>
+      </c>
+      <c r="J48" s="12" t="inlineStr">
+        <is>
+          <t>объем</t>
+        </is>
+      </c>
+      <c r="K48" s="14" t="n">
+        <v>213</v>
+      </c>
+      <c r="L48" s="14" t="n">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr"/>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>20 футов, 22 т</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="n">
+        <v>6.216806035301278</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>152</v>
+      </c>
+      <c r="E49" s="13" t="n">
+        <v>6.369117783166159</v>
+      </c>
+      <c r="F49" s="17" t="n">
+        <v>0.28950535378028</v>
+      </c>
+      <c r="G49" s="14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H49" s="13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I49" s="17" t="n">
+        <v>0.2011390367041068</v>
+      </c>
+      <c r="J49" s="12" t="inlineStr">
+        <is>
+          <t>груз кончился</t>
+        </is>
+      </c>
+      <c r="K49" s="14" t="n">
+        <v>76</v>
+      </c>
+      <c r="L49" s="14" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>Сорокафутовый и двадцатифутовый</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>40 футов, 26 т</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="n">
+        <v>25.3741099432722</v>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>622</v>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>25.99577563688237</v>
+      </c>
+      <c r="F50" s="16" t="n">
+        <v>0.9998375244954757</v>
+      </c>
+      <c r="G50" s="14" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="H50" s="13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I50" s="17" t="n">
+        <v>0.5703957417859358</v>
+      </c>
+      <c r="J50" s="12" t="inlineStr">
+        <is>
+          <t>вес</t>
+        </is>
+      </c>
+      <c r="K50" s="14" t="n">
+        <v>283</v>
+      </c>
+      <c r="L50" s="14" t="n">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr"/>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>20 футов, 22 т</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="n">
+        <v>1.924473236317661</v>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="E51" s="13" t="n">
+        <v>1.971622830607444</v>
+      </c>
+      <c r="F51" s="17" t="n">
+        <v>0.08961921957306564</v>
+      </c>
+      <c r="G51" s="14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H51" s="13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I51" s="17" t="n">
+        <v>0.03958656252336723</v>
+      </c>
+      <c r="J51" s="12" t="inlineStr">
+        <is>
+          <t>груз кончился</t>
+        </is>
+      </c>
+      <c r="K51" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="L51" s="14" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Доска: сколько покупать</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>— Два двадцатифутовых по 22 т: 0.96 куб. м, это 48 досок 4 м х 200 х 25 и 669 кг веса, которые занимают место груза.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>— Один усиленный двадцатифутовый: 0.74 куб. м, это 37 досок 4 м х 200 х 25 и 517 кг веса, которые занимают место груза.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>— Один сорокафутовый: 0.89 куб. м, это 44 досок 4 м х 200 х 25 и 622 кг веса, которые занимают место груза.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>Выводы</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>— Чтобы увезти всю арматуру  дешевле всего «Два двадцатифутовых по 22 т»: 632 000 руб против 929 978 у худшего варианта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
-        <is>
-          <t>— Два двадцатифутовых дороже сорокафутового по расходам на 71 000 руб  но увозят на 1.94 т больше и не оставляют ничего. Через транспортную компанию эти тонны стоили бы 157 502 руб.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>— Один двадцатифутовый самый дешевый по ставке — 290 000 руб  и самая низкая цена тонны 15 131. Но он оставляет 6.02 т  и если их везти транспортной компанией  вариант становится худшим: 831 403 руб.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>— Усиленный двадцатифутовый бессмыслен при любом раскладе: он того же размера, что обычный, объем кончается на тех же тоннах, а стоит на 79 тысяч дороже.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="16" t="inlineStr">
-        <is>
-          <t>— Доска съедает 621 кг в сорокафутовом и по 521 кг в каждом двадцатифутовом. Это не мелочь: в двадцатифутовом полтонны доски это полтонны неувезенной арматуры.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="16" t="inlineStr">
-        <is>
-          <t>— Автодоставка добавляет 54 тысячи на двадцатифутовый и 74 на сорокафутовый, считая оба конца. На двух контейнерах это 108 тысяч — больше, чем разница в ставке за сами контейнеры.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="16" t="inlineStr">
-        <is>
-          <t>— Погрузка на двух двадцатифутовых стоит 52 000 руб против 32 000 на сорокафутовом. Разница всего 20 000 руб  и только потому  что оба контейнера грузим в один день и подачу погрузчика платим один раз. Разными днями это 64 000 руб.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>— У сорокафутового погрузка не заканчивается контейнером: 1.94 т остатка надо грузить отдельным днем  это еще одна подача погрузчика и бригада — 22 000 руб сверх тарифа ТК.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="A48" s="16" t="inlineStr">
-        <is>
-          <t>— Выгрузка в Петербурге в расчет не входит: ставок на тамошний погрузчик и грузчиков у нас нет. По владивостокским это около 32 000 руб на контейнер  и считать надо отдельно.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="16" t="inlineStr">
-        <is>
-          <t>— Сохранность груза тоже за два двадцатифутовых: при равной развеске в каждом едет около 13,7 т вместо 25, пирог ниже, на нижние задвижки давит вдвое меньше, и мелочь не оказывается под тяжелым. Разбивку считает build_two_containers.py.</t>
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>— Усиленный двадцатифутовый паспортно берет 27 т, но до них не догружается: внутри те же 33 куб. м. Даже если грузить самое плотное вперед, в него входит 25.21 т груза плюс 618 кг доски — 25.82 т брутто, и объем кончается. Паспортной грузоподъемности не хватает 1.18 т до предела.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>— В нашей очередности, с крупными клинкетами первыми, в усиленный входит еще меньше — 21.08 т. Клинкеты самые объемные на тонну: 530 кг в кубометре против 967 у средней арматуры. Чем раньше они грузятся, тем меньше тонн в корпус.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>— Доска не бесплатная ни по весу, ни по месту: 618 кг и 0.88 куб. м в усиленном. Это те же полтонны неувезенной арматуры, и считать ее надо от фактического веса, а не от паспортного.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>— По деньгам в нашей очередности дешевле всего «Два двадцатифутовых по 22 т»: 632 000 руб против 926 561 у худшего варианта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>— Два обычных двадцатифутовых увозят 27.30 т и не оставляют ничего. Сорокафутовый — 25.37 т  остаток 1.92 т через транспортную компанию стоит 155 882 руб плюс отдельный день погрузки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="18" t="inlineStr">
+        <is>
+          <t>— Сорокафутовый при этом загружен по объему примерно наполовину: у него упор в вес, а не в место. У любого двадцатифутового наоборот.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>— Выгрузка в Петербурге в расчет не входит: ставок на тамошний погрузчик и грузчиков нет. По владивостокским это около 32 000 руб на контейнер.</t>
         </is>
       </c>
     </row>

--- a/outputs/marine_equipment/Логистика_варианты.xlsx
+++ b/outputs/marine_equipment/Логистика_варианты.xlsx
@@ -115,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -138,6 +138,7 @@
     <xf numFmtId="3" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -506,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -804,140 +805,138 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Два двадцатифутовых по 22 т</t>
+          <t>Усиленный двадцатифутовый, 27 т по весу</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>27.29858317958968</v>
+        <v>26.35080994327219</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>669</v>
+        <v>646</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>27.96739846748962</v>
+        <v>26.99640478688236</v>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>груз кончился, объем</t>
+          <t>вес</t>
         </is>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0</v>
+        <v>0.9477732363176621</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>580000</v>
+        <v>369000</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>52000</v>
+        <v>32000</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="11" t="n"/>
+        <v>76769.63214173063</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>22000</v>
+      </c>
       <c r="L23" s="11" t="n">
-        <v>632000</v>
+        <v>499769.6321417306</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>23151.38466499343</v>
+        <v>15217.74855737905</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Один усиленный двадцатифутовый</t>
+          <t>Два усиленных по 27 т</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>21.0817771442884</v>
+        <v>27.29858317958985</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>517</v>
+        <v>669</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>21.59828068432347</v>
+        <v>27.9673984674898</v>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>объем</t>
+          <t>вес, груз кончился</t>
         </is>
       </c>
       <c r="G24" s="13" t="n">
-        <v>6.216806035301273</v>
+        <v>0</v>
       </c>
       <c r="H24" s="14" t="n">
-        <v>369000</v>
+        <v>738000</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>32000</v>
+        <v>52000</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>503561.2888594032</v>
-      </c>
-      <c r="K24" s="14" t="n">
-        <v>22000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K24" s="14" t="n"/>
       <c r="L24" s="15" t="n">
-        <v>926561.2888594032</v>
+        <v>790000</v>
       </c>
       <c r="M24" s="14" t="n">
-        <v>19021.16682362527</v>
+        <v>28939.2308312416</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Один сорокафутовый</t>
+          <t>Два двадцатифутовых по 22 т</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>25.3741099432722</v>
+        <v>27.29858317958968</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>622</v>
+        <v>669</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>25.99577563688237</v>
+        <v>27.96739846748962</v>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>вес</t>
+          <t>груз кончился, объем</t>
         </is>
       </c>
       <c r="G25" s="13" t="n">
-        <v>1.924473236317662</v>
+        <v>0</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>509000</v>
+        <v>580000</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>32000</v>
+        <v>52000</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>155882.3321417306</v>
-      </c>
-      <c r="K25" s="14" t="n">
-        <v>22000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K25" s="14" t="n"/>
       <c r="L25" s="15" t="n">
-        <v>718882.3321417306</v>
+        <v>632000</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>21320.94490051041</v>
+        <v>23151.38466499343</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Один двадцатифутовый 22 т</t>
+          <t>Один усиленный двадцатифутовый</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
@@ -961,7 +960,7 @@
         <v>6.216806035301273</v>
       </c>
       <c r="H26" s="14" t="n">
-        <v>290000</v>
+        <v>369000</v>
       </c>
       <c r="I26" s="14" t="n">
         <v>32000</v>
@@ -973,799 +972,805 @@
         <v>22000</v>
       </c>
       <c r="L26" s="15" t="n">
-        <v>847561.2888594032</v>
+        <v>926561.2888594032</v>
       </c>
       <c r="M26" s="14" t="n">
-        <v>15273.8546563774</v>
+        <v>19021.16682362527</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Усиленный и обычный двадцатифутовые</t>
+          <t>Один сорокафутовый</t>
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>27.29858317958968</v>
+        <v>25.3741099432722</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>669</v>
+        <v>622</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>27.96739846748962</v>
+        <v>25.99577563688237</v>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>груз кончился, объем</t>
+          <t>вес</t>
         </is>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0</v>
+        <v>1.924473236317662</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>659000</v>
+        <v>509000</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>64000</v>
+        <v>32000</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="14" t="n"/>
+        <v>155882.3321417306</v>
+      </c>
+      <c r="K27" s="14" t="n">
+        <v>22000</v>
+      </c>
       <c r="L27" s="15" t="n">
-        <v>723000</v>
+        <v>718882.3321417306</v>
       </c>
       <c r="M27" s="14" t="n">
-        <v>26484.89100125039</v>
+        <v>21320.94490051041</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
+          <t>Один двадцатифутовый 22 т</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>21.0817771442884</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>517</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>21.59828068432347</v>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>объем</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>6.216806035301273</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>290000</v>
+      </c>
+      <c r="I28" s="14" t="n">
+        <v>32000</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>503561.2888594032</v>
+      </c>
+      <c r="K28" s="14" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L28" s="15" t="n">
+        <v>847561.2888594032</v>
+      </c>
+      <c r="M28" s="14" t="n">
+        <v>15273.8546563774</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Усиленный и обычный двадцатифутовые</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>27.29858317958968</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>669</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>27.96739846748962</v>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>груз кончился, объем</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>659000</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>64000</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="14" t="n"/>
+      <c r="L29" s="15" t="n">
+        <v>723000</v>
+      </c>
+      <c r="M29" s="14" t="n">
+        <v>26484.89100125039</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
           <t>Сорокафутовый и двадцатифутовый</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n">
+      <c r="B30" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="13" t="n">
+      <c r="C30" s="13" t="n">
         <v>27.29858317958986</v>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D30" s="14" t="n">
         <v>669</v>
       </c>
-      <c r="E28" s="13" t="n">
+      <c r="E30" s="13" t="n">
         <v>27.96739846748982</v>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>вес, груз кончился</t>
         </is>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="G30" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="14" t="n">
+      <c r="H30" s="14" t="n">
         <v>799000</v>
       </c>
-      <c r="I28" s="14" t="n">
+      <c r="I30" s="14" t="n">
         <v>64000</v>
       </c>
-      <c r="J28" s="14" t="n">
+      <c r="J30" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K28" s="14" t="n"/>
-      <c r="L28" s="15" t="n">
+      <c r="K30" s="14" t="n"/>
+      <c r="L30" s="15" t="n">
         <v>863000</v>
       </c>
-      <c r="M28" s="14" t="n">
+      <c r="M30" s="14" t="n">
         <v>31613.36228779936</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Самое плотное вперед</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Теоретический максимум тонн в корпус. Так грузить нельзя: плотное — это мелочь в ящиках, а крупные клинкеты, которые покупатель просил первыми, самые объемные и уехали бы последними.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="44" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="35" ht="44" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Корпусов</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>Увезет груза, т</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>Доска, кг</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>Брутто, т</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t>Во что уперся</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>Останется, т</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>Контейнеры и авто, руб</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>Погрузка, руб</t>
         </is>
       </c>
-      <c r="J33" s="8" t="inlineStr">
+      <c r="J35" s="8" t="inlineStr">
         <is>
           <t>Остаток через ТК, руб</t>
         </is>
       </c>
-      <c r="K33" s="8" t="inlineStr">
+      <c r="K35" s="8" t="inlineStr">
         <is>
           <t>Погрузка остатка, руб</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L35" s="8" t="inlineStr">
         <is>
           <t>ВСЕГО, руб</t>
         </is>
       </c>
-      <c r="M33" s="8" t="inlineStr">
+      <c r="M35" s="8" t="inlineStr">
         <is>
           <t>Руб за увезенную тонну</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>Два двадцатифутовых по 22 т</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C34" s="13" t="n">
-        <v>27.29858317958847</v>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>669</v>
-      </c>
-      <c r="E34" s="13" t="n">
-        <v>27.96739846748839</v>
-      </c>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>вес, груз кончился</t>
-        </is>
-      </c>
-      <c r="G34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="14" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I34" s="14" t="n">
-        <v>52000</v>
-      </c>
-      <c r="J34" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="14" t="n"/>
-      <c r="L34" s="15" t="n">
-        <v>632000</v>
-      </c>
-      <c r="M34" s="14" t="n">
-        <v>23151.38466499445</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>Один усиленный двадцатифутовый</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="n">
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Усиленный двадцатифутовый, 27 т по весу</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="10" t="n">
-        <v>25.20501317784694</v>
-      </c>
-      <c r="D35" s="11" t="n">
-        <v>618</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>25.82253600070419</v>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>объем</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="n">
-        <v>2.093570001741579</v>
-      </c>
-      <c r="H35" s="11" t="n">
+      <c r="C36" s="10" t="n">
+        <v>26.3541957647492</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>646</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>26.99987356098555</v>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>вес</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>0.9443874148394101</v>
+      </c>
+      <c r="H36" s="11" t="n">
         <v>369000</v>
       </c>
-      <c r="I35" s="11" t="n">
+      <c r="I36" s="11" t="n">
         <v>32000</v>
       </c>
-      <c r="J35" s="11" t="n">
-        <v>169579.1701410679</v>
-      </c>
-      <c r="K35" s="11" t="n">
+      <c r="J36" s="11" t="n">
+        <v>76495.38060199222</v>
+      </c>
+      <c r="K36" s="11" t="n">
         <v>22000</v>
       </c>
-      <c r="L35" s="11" t="n">
-        <v>592579.1701410678</v>
-      </c>
-      <c r="M35" s="11" t="n">
-        <v>15909.53343965894</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Один сорокафутовый</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="13" t="n">
-        <v>25.37798218937958</v>
-      </c>
-      <c r="D36" s="14" t="n">
-        <v>622</v>
-      </c>
-      <c r="E36" s="13" t="n">
-        <v>25.99974275301938</v>
-      </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>вес</t>
-        </is>
-      </c>
-      <c r="G36" s="13" t="n">
-        <v>1.920600990208946</v>
-      </c>
-      <c r="H36" s="14" t="n">
-        <v>509000</v>
-      </c>
-      <c r="I36" s="14" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J36" s="14" t="n">
-        <v>155568.6802069246</v>
-      </c>
-      <c r="K36" s="14" t="n">
-        <v>22000</v>
-      </c>
-      <c r="L36" s="15" t="n">
-        <v>718568.6802069247</v>
-      </c>
-      <c r="M36" s="14" t="n">
-        <v>21317.69168891619</v>
+      <c r="L36" s="11" t="n">
+        <v>499495.3806019922</v>
+      </c>
+      <c r="M36" s="11" t="n">
+        <v>15215.79347666412</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Один двадцатифутовый 22 т</t>
+          <t>Два усиленных по 27 т</t>
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>21.47385505985811</v>
+        <v>27.29858317958861</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>526</v>
+        <v>669</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>21.99996450882463</v>
+        <v>27.96739846748853</v>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>вес</t>
+          <t>вес, груз кончился</t>
         </is>
       </c>
       <c r="G37" s="13" t="n">
-        <v>5.824728119730372</v>
+        <v>0</v>
       </c>
       <c r="H37" s="14" t="n">
-        <v>290000</v>
+        <v>738000</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>32000</v>
+        <v>52000</v>
       </c>
       <c r="J37" s="14" t="n">
-        <v>471802.9776981601</v>
-      </c>
-      <c r="K37" s="14" t="n">
-        <v>22000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K37" s="14" t="n"/>
       <c r="L37" s="15" t="n">
-        <v>815802.9776981601</v>
+        <v>790000</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>14994.97873588273</v>
+        <v>28939.23083124292</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>Усиленный и обычный двадцатифутовые</t>
+          <t>Два двадцатифутовых по 22 т</t>
         </is>
       </c>
       <c r="B38" s="12" t="n">
         <v>2</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>27.29858317958852</v>
+        <v>27.29858317958847</v>
       </c>
       <c r="D38" s="14" t="n">
         <v>669</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>27.96739846748843</v>
+        <v>27.96739846748839</v>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>груз кончился, объем</t>
+          <t>вес, груз кончился</t>
         </is>
       </c>
       <c r="G38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="14" t="n">
-        <v>659000</v>
+        <v>580000</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>64000</v>
+        <v>52000</v>
       </c>
       <c r="J38" s="14" t="n">
         <v>0</v>
       </c>
       <c r="K38" s="14" t="n"/>
       <c r="L38" s="15" t="n">
-        <v>723000</v>
+        <v>632000</v>
       </c>
       <c r="M38" s="14" t="n">
-        <v>26484.89100125152</v>
+        <v>23151.38466499445</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Сорокафутовый и двадцатифутовый</t>
+          <t>Один усиленный двадцатифутовый</t>
         </is>
       </c>
       <c r="B39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>25.20501317784694</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>618</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>25.82253600070419</v>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>объем</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>2.093570001741579</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>369000</v>
+      </c>
+      <c r="I39" s="14" t="n">
+        <v>32000</v>
+      </c>
+      <c r="J39" s="14" t="n">
+        <v>169579.1701410679</v>
+      </c>
+      <c r="K39" s="14" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L39" s="15" t="n">
+        <v>592579.1701410678</v>
+      </c>
+      <c r="M39" s="14" t="n">
+        <v>15909.53343965894</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Один сорокафутовый</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="13" t="n">
+        <v>25.37798218937958</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>622</v>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>25.99974275301938</v>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>вес</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>1.920600990208946</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>509000</v>
+      </c>
+      <c r="I40" s="14" t="n">
+        <v>32000</v>
+      </c>
+      <c r="J40" s="14" t="n">
+        <v>155568.6802069246</v>
+      </c>
+      <c r="K40" s="14" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L40" s="15" t="n">
+        <v>718568.6802069247</v>
+      </c>
+      <c r="M40" s="14" t="n">
+        <v>21317.69168891619</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Один двадцатифутовый 22 т</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>21.47385505985811</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>526</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>21.99996450882463</v>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>вес</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>5.824728119730372</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>290000</v>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>32000</v>
+      </c>
+      <c r="J41" s="14" t="n">
+        <v>471802.9776981601</v>
+      </c>
+      <c r="K41" s="14" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L41" s="15" t="n">
+        <v>815802.9776981601</v>
+      </c>
+      <c r="M41" s="14" t="n">
+        <v>14994.97873588273</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Усиленный и обычный двадцатифутовые</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="13" t="n">
-        <v>27.29858317958853</v>
-      </c>
-      <c r="D39" s="14" t="n">
+      <c r="C42" s="13" t="n">
+        <v>27.29858317958852</v>
+      </c>
+      <c r="D42" s="14" t="n">
         <v>669</v>
       </c>
-      <c r="E39" s="13" t="n">
-        <v>27.96739846748845</v>
-      </c>
-      <c r="F39" s="12" t="inlineStr">
-        <is>
-          <t>вес, груз кончился</t>
-        </is>
-      </c>
-      <c r="G39" s="13" t="n">
+      <c r="E42" s="13" t="n">
+        <v>27.96739846748843</v>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>груз кончился, объем</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="14" t="n">
-        <v>799000</v>
-      </c>
-      <c r="I39" s="14" t="n">
+      <c r="H42" s="14" t="n">
+        <v>659000</v>
+      </c>
+      <c r="I42" s="14" t="n">
         <v>64000</v>
       </c>
-      <c r="J39" s="14" t="n">
+      <c r="J42" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K39" s="14" t="n"/>
-      <c r="L39" s="15" t="n">
-        <v>863000</v>
-      </c>
-      <c r="M39" s="14" t="n">
-        <v>31613.3622878009</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Что в каждом корпусе — по очередности покупателя</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Корпус</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>Груз, т</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Доска, кг</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>Брутто, т</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>Из лимита</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>Объем груза, куб. м</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>Доска, куб. м</t>
-        </is>
-      </c>
-      <c r="I42" s="8" t="inlineStr">
-        <is>
-          <t>Объем занят</t>
-        </is>
-      </c>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t>Во что уперся</t>
-        </is>
-      </c>
-      <c r="K42" s="8" t="inlineStr">
-        <is>
-          <t>Позиций</t>
-        </is>
-      </c>
-      <c r="L42" s="8" t="inlineStr">
-        <is>
-          <t>Штук</t>
-        </is>
+      <c r="K42" s="14" t="n"/>
+      <c r="L42" s="15" t="n">
+        <v>723000</v>
+      </c>
+      <c r="M42" s="14" t="n">
+        <v>26484.89100125152</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Два двадцатифутовых по 22 т</t>
-        </is>
-      </c>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>20 футов, 22 т</t>
-        </is>
+          <t>Сорокафутовый и двадцатифутовый</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>21.0817771442884</v>
+        <v>27.29858317958853</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>517</v>
+        <v>669</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>21.59828068432347</v>
-      </c>
-      <c r="F43" s="16" t="n">
-        <v>0.981740031105612</v>
-      </c>
-      <c r="G43" s="14" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="H43" s="13" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I43" s="16" t="n">
-        <v>0.9999806727288048</v>
-      </c>
-      <c r="J43" s="12" t="inlineStr">
-        <is>
-          <t>объем</t>
-        </is>
-      </c>
-      <c r="K43" s="14" t="n">
-        <v>213</v>
-      </c>
-      <c r="L43" s="14" t="n">
-        <v>2573</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="inlineStr"/>
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>20 футов, 22 т</t>
-        </is>
-      </c>
-      <c r="C44" s="13" t="n">
-        <v>6.216806035301278</v>
-      </c>
-      <c r="D44" s="14" t="n">
-        <v>152</v>
-      </c>
-      <c r="E44" s="13" t="n">
-        <v>6.369117783166159</v>
-      </c>
-      <c r="F44" s="17" t="n">
-        <v>0.28950535378028</v>
-      </c>
-      <c r="G44" s="14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H44" s="13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I44" s="17" t="n">
-        <v>0.2011390367041068</v>
-      </c>
-      <c r="J44" s="12" t="inlineStr">
-        <is>
-          <t>груз кончился</t>
-        </is>
-      </c>
-      <c r="K44" s="14" t="n">
-        <v>76</v>
-      </c>
-      <c r="L44" s="14" t="n">
-        <v>330</v>
+        <v>27.96739846748845</v>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>вес, груз кончился</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>799000</v>
+      </c>
+      <c r="I43" s="14" t="n">
+        <v>64000</v>
+      </c>
+      <c r="J43" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="14" t="n"/>
+      <c r="L43" s="15" t="n">
+        <v>863000</v>
+      </c>
+      <c r="M43" s="14" t="n">
+        <v>31613.3622878009</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>Один усиленный двадцатифутовый</t>
-        </is>
-      </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>20 футов усиленный, 27 т</t>
-        </is>
-      </c>
-      <c r="C45" s="13" t="n">
-        <v>21.0817771442884</v>
-      </c>
-      <c r="D45" s="14" t="n">
-        <v>517</v>
-      </c>
-      <c r="E45" s="13" t="n">
-        <v>21.59828068432347</v>
-      </c>
-      <c r="F45" s="17" t="n">
-        <v>0.7999363216416098</v>
-      </c>
-      <c r="G45" s="14" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="H45" s="13" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I45" s="16" t="n">
-        <v>0.9999806727288048</v>
-      </c>
-      <c r="J45" s="12" t="inlineStr">
-        <is>
-          <t>объем</t>
-        </is>
-      </c>
-      <c r="K45" s="14" t="n">
-        <v>213</v>
-      </c>
-      <c r="L45" s="14" t="n">
-        <v>2573</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>Один сорокафутовый</t>
-        </is>
-      </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>40 футов, 26 т</t>
-        </is>
-      </c>
-      <c r="C46" s="13" t="n">
-        <v>25.3741099432722</v>
-      </c>
-      <c r="D46" s="14" t="n">
-        <v>622</v>
-      </c>
-      <c r="E46" s="13" t="n">
-        <v>25.99577563688237</v>
-      </c>
-      <c r="F46" s="16" t="n">
-        <v>0.9998375244954757</v>
-      </c>
-      <c r="G46" s="14" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="H46" s="13" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I46" s="17" t="n">
-        <v>0.5703957417859358</v>
-      </c>
-      <c r="J46" s="12" t="inlineStr">
-        <is>
-          <t>вес</t>
-        </is>
-      </c>
-      <c r="K46" s="14" t="n">
-        <v>283</v>
-      </c>
-      <c r="L46" s="14" t="n">
-        <v>2856</v>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Что в каждом корпусе — по очередности покупателя</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Корпус</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Груз, т</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Доска, кг</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>Брутто, т</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Из лимита</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>Объем груза, куб. м</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>Доска, куб. м</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>Объем занят</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>Во что уперся</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>Позиций</t>
+        </is>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>Штук</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>Один двадцатифутовый 22 т</t>
+          <t>Усиленный двадцатифутовый, 27 т по весу</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>20 футов, 22 т</t>
+          <t>20 футов усиленный, 27 т по весу</t>
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>21.0817771442884</v>
+        <v>26.35080994327219</v>
       </c>
       <c r="D47" s="14" t="n">
-        <v>517</v>
+        <v>646</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>21.59828068432347</v>
+        <v>26.99640478688236</v>
       </c>
       <c r="F47" s="16" t="n">
-        <v>0.981740031105612</v>
+        <v>0.9998668439586058</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>32.3</v>
+        <v>37.9</v>
       </c>
       <c r="H47" s="13" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I47" s="16" t="n">
-        <v>0.9999806727288048</v>
+        <v>0.92</v>
+      </c>
+      <c r="I47" s="17" t="n">
+        <v>3.884877834801491e-08</v>
       </c>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>объем</t>
+          <t>вес</t>
         </is>
       </c>
       <c r="K47" s="14" t="n">
-        <v>213</v>
+        <v>283</v>
       </c>
       <c r="L47" s="14" t="n">
-        <v>2573</v>
+        <v>2872</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Усиленный и обычный двадцатифутовые</t>
+          <t>Два усиленных по 27 т</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>20 футов усиленный, 27 т</t>
+          <t>20 футов усиленный, 27 т по весу</t>
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>21.0817771442884</v>
+        <v>26.35080994327219</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>517</v>
+        <v>646</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>21.59828068432347</v>
-      </c>
-      <c r="F48" s="17" t="n">
-        <v>0.7999363216416098</v>
+        <v>26.99640478688236</v>
+      </c>
+      <c r="F48" s="16" t="n">
+        <v>0.9998668439586058</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>32.3</v>
+        <v>37.9</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I48" s="16" t="n">
-        <v>0.9999806727288048</v>
+        <v>0.92</v>
+      </c>
+      <c r="I48" s="17" t="n">
+        <v>3.884877834801491e-08</v>
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>объем</t>
+          <t>вес</t>
         </is>
       </c>
       <c r="K48" s="14" t="n">
-        <v>213</v>
+        <v>283</v>
       </c>
       <c r="L48" s="14" t="n">
-        <v>2573</v>
+        <v>2872</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr"/>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>20 футов, 22 т</t>
+          <t>20 футов усиленный, 27 т по весу</t>
         </is>
       </c>
       <c r="C49" s="13" t="n">
-        <v>6.216806035301278</v>
+        <v>0.9477732363176619</v>
       </c>
       <c r="D49" s="14" t="n">
-        <v>152</v>
+        <v>23</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>6.369117783166159</v>
+        <v>0.9709936806074445</v>
       </c>
       <c r="F49" s="17" t="n">
-        <v>0.28950535378028</v>
+        <v>0.03596272891138683</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>6.4</v>
+        <v>0.8</v>
       </c>
       <c r="H49" s="13" t="n">
-        <v>0.22</v>
+        <v>0.03</v>
       </c>
       <c r="I49" s="17" t="n">
-        <v>0.2011390367041068</v>
+        <v>7.881720632711185e-10</v>
       </c>
       <c r="J49" s="12" t="inlineStr">
         <is>
@@ -1773,54 +1778,54 @@
         </is>
       </c>
       <c r="K49" s="14" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="L49" s="14" t="n">
-        <v>330</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>Сорокафутовый и двадцатифутовый</t>
+          <t>Два двадцатифутовых по 22 т</t>
         </is>
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>40 футов, 26 т</t>
+          <t>20 футов, 22 т</t>
         </is>
       </c>
       <c r="C50" s="13" t="n">
-        <v>25.3741099432722</v>
+        <v>21.0817771442884</v>
       </c>
       <c r="D50" s="14" t="n">
-        <v>622</v>
+        <v>517</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>25.99577563688237</v>
+        <v>21.59828068432347</v>
       </c>
       <c r="F50" s="16" t="n">
-        <v>0.9998375244954757</v>
+        <v>0.981740031105612</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>37.4</v>
+        <v>32.3</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I50" s="17" t="n">
-        <v>0.5703957417859358</v>
+        <v>0.74</v>
+      </c>
+      <c r="I50" s="16" t="n">
+        <v>0.9999806727288048</v>
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>вес</t>
+          <t>объем</t>
         </is>
       </c>
       <c r="K50" s="14" t="n">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="L50" s="14" t="n">
-        <v>2856</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="51">
@@ -1831,117 +1836,617 @@
         </is>
       </c>
       <c r="C51" s="13" t="n">
+        <v>6.216806035301278</v>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>152</v>
+      </c>
+      <c r="E51" s="13" t="n">
+        <v>6.369117783166159</v>
+      </c>
+      <c r="F51" s="17" t="n">
+        <v>0.28950535378028</v>
+      </c>
+      <c r="G51" s="14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H51" s="13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I51" s="17" t="n">
+        <v>0.2011390367041068</v>
+      </c>
+      <c r="J51" s="12" t="inlineStr">
+        <is>
+          <t>груз кончился</t>
+        </is>
+      </c>
+      <c r="K51" s="14" t="n">
+        <v>76</v>
+      </c>
+      <c r="L51" s="14" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>Один усиленный двадцатифутовый</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>20 футов усиленный, 27 т</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="n">
+        <v>21.0817771442884</v>
+      </c>
+      <c r="D52" s="14" t="n">
+        <v>517</v>
+      </c>
+      <c r="E52" s="13" t="n">
+        <v>21.59828068432347</v>
+      </c>
+      <c r="F52" s="17" t="n">
+        <v>0.7999363216416098</v>
+      </c>
+      <c r="G52" s="14" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="H52" s="13" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I52" s="16" t="n">
+        <v>0.9999806727288048</v>
+      </c>
+      <c r="J52" s="12" t="inlineStr">
+        <is>
+          <t>объем</t>
+        </is>
+      </c>
+      <c r="K52" s="14" t="n">
+        <v>213</v>
+      </c>
+      <c r="L52" s="14" t="n">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>Один сорокафутовый</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>40 футов, 26 т</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="n">
+        <v>25.3741099432722</v>
+      </c>
+      <c r="D53" s="14" t="n">
+        <v>622</v>
+      </c>
+      <c r="E53" s="13" t="n">
+        <v>25.99577563688237</v>
+      </c>
+      <c r="F53" s="16" t="n">
+        <v>0.9998375244954757</v>
+      </c>
+      <c r="G53" s="14" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="H53" s="13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I53" s="17" t="n">
+        <v>0.5703957417859358</v>
+      </c>
+      <c r="J53" s="12" t="inlineStr">
+        <is>
+          <t>вес</t>
+        </is>
+      </c>
+      <c r="K53" s="14" t="n">
+        <v>283</v>
+      </c>
+      <c r="L53" s="14" t="n">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>Один двадцатифутовый 22 т</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>20 футов, 22 т</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="n">
+        <v>21.0817771442884</v>
+      </c>
+      <c r="D54" s="14" t="n">
+        <v>517</v>
+      </c>
+      <c r="E54" s="13" t="n">
+        <v>21.59828068432347</v>
+      </c>
+      <c r="F54" s="16" t="n">
+        <v>0.981740031105612</v>
+      </c>
+      <c r="G54" s="14" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="H54" s="13" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I54" s="16" t="n">
+        <v>0.9999806727288048</v>
+      </c>
+      <c r="J54" s="12" t="inlineStr">
+        <is>
+          <t>объем</t>
+        </is>
+      </c>
+      <c r="K54" s="14" t="n">
+        <v>213</v>
+      </c>
+      <c r="L54" s="14" t="n">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Усиленный и обычный двадцатифутовые</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>20 футов усиленный, 27 т</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="n">
+        <v>21.0817771442884</v>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>517</v>
+      </c>
+      <c r="E55" s="13" t="n">
+        <v>21.59828068432347</v>
+      </c>
+      <c r="F55" s="17" t="n">
+        <v>0.7999363216416098</v>
+      </c>
+      <c r="G55" s="14" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="H55" s="13" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I55" s="16" t="n">
+        <v>0.9999806727288048</v>
+      </c>
+      <c r="J55" s="12" t="inlineStr">
+        <is>
+          <t>объем</t>
+        </is>
+      </c>
+      <c r="K55" s="14" t="n">
+        <v>213</v>
+      </c>
+      <c r="L55" s="14" t="n">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr"/>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>20 футов, 22 т</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="n">
+        <v>6.216806035301278</v>
+      </c>
+      <c r="D56" s="14" t="n">
+        <v>152</v>
+      </c>
+      <c r="E56" s="13" t="n">
+        <v>6.369117783166159</v>
+      </c>
+      <c r="F56" s="17" t="n">
+        <v>0.28950535378028</v>
+      </c>
+      <c r="G56" s="14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H56" s="13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I56" s="17" t="n">
+        <v>0.2011390367041068</v>
+      </c>
+      <c r="J56" s="12" t="inlineStr">
+        <is>
+          <t>груз кончился</t>
+        </is>
+      </c>
+      <c r="K56" s="14" t="n">
+        <v>76</v>
+      </c>
+      <c r="L56" s="14" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>Сорокафутовый и двадцатифутовый</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>40 футов, 26 т</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="n">
+        <v>25.3741099432722</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>622</v>
+      </c>
+      <c r="E57" s="13" t="n">
+        <v>25.99577563688237</v>
+      </c>
+      <c r="F57" s="16" t="n">
+        <v>0.9998375244954757</v>
+      </c>
+      <c r="G57" s="14" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="H57" s="13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I57" s="17" t="n">
+        <v>0.5703957417859358</v>
+      </c>
+      <c r="J57" s="12" t="inlineStr">
+        <is>
+          <t>вес</t>
+        </is>
+      </c>
+      <c r="K57" s="14" t="n">
+        <v>283</v>
+      </c>
+      <c r="L57" s="14" t="n">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr"/>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>20 футов, 22 т</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="n">
         <v>1.924473236317661</v>
       </c>
-      <c r="D51" s="14" t="n">
+      <c r="D58" s="14" t="n">
         <v>47</v>
       </c>
-      <c r="E51" s="13" t="n">
+      <c r="E58" s="13" t="n">
         <v>1.971622830607444</v>
       </c>
-      <c r="F51" s="17" t="n">
+      <c r="F58" s="17" t="n">
         <v>0.08961921957306564</v>
       </c>
-      <c r="G51" s="14" t="n">
+      <c r="G58" s="14" t="n">
         <v>1.2</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="H58" s="13" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="I51" s="17" t="n">
+      <c r="I58" s="17" t="n">
         <v>0.03958656252336723</v>
       </c>
-      <c r="J51" s="12" t="inlineStr">
+      <c r="J58" s="12" t="inlineStr">
         <is>
           <t>груз кончился</t>
         </is>
       </c>
-      <c r="K51" s="14" t="n">
+      <c r="K58" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="L51" s="14" t="n">
+      <c r="L58" s="14" t="n">
         <v>47</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>Доска: сколько покупать</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>— Усиленный двадцатифутовый, 27 т по весу: 0.92 куб. м, это 46 досок 4 м х 200 х 25 и 646 кг веса, которые занимают место груза.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>— Два усиленных по 27 т: 0.96 куб. м, это 48 досок 4 м х 200 х 25 и 669 кг веса, которые занимают место груза.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>— Два двадцатифутовых по 22 т: 0.96 куб. м, это 48 досок 4 м х 200 х 25 и 669 кг веса, которые занимают место груза.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>— Один усиленный двадцатифутовый: 0.74 куб. м, это 37 досок 4 м х 200 х 25 и 517 кг веса, которые занимают место груза.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>— Один сорокафутовый: 0.89 куб. м, это 44 досок 4 м х 200 х 25 и 622 кг веса, которые занимают место груза.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Усиленный двадцатифутовый на 27 т: все расходы</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Контейнер усиленный, 20 футов</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="n">
+        <v>315000</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>ставка на руках</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Автодоставка во Владивостоке</t>
+        </is>
+      </c>
+      <c r="B67" s="18" t="n">
+        <v>27000</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>подача под погрузку</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Автодоставка в Петербурге</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="n">
+        <v>27000</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>вывоз с терминала, ставка подтверждена</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Погрузка: погрузчик и грузчики</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="n">
+        <v>32000</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>подача 12 000 + 4 ч x 2 000 + 4 грузчика x 4 ч x 750</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>ИТОГО за контейнер</t>
+        </is>
+      </c>
+      <c r="B70" s="18" t="n">
+        <v>401000</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Увезет груза, кг</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="n">
+        <v>26351</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>плюс доска, вместе ровно 27 т брутто</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Доска, кг</t>
+        </is>
+      </c>
+      <c r="B72" s="18" t="n">
+        <v>646</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>0.92 куб. м, 46 досок 4 м</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Останется во Владивостоке, кг</t>
+        </is>
+      </c>
+      <c r="B73" s="18" t="n">
+        <v>948</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>5 позиций</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Остаток транспортной компанией</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="n">
+        <v>76770</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>81 руб за кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Погрузка остатка</t>
+        </is>
+      </c>
+      <c r="B75" s="18" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>отдельный день</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>ВСЕГО с остатком через ТК</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="n">
+        <v>499770</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>ВСЕГО без остатка</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="n">
+        <v>401000</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>остаток — позиции без согласованной цены, по договору они не считаются проданными и ехать не должны</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>Вариант считает усиленный по паспортным 27 тоннам: ограничение по объему снято. Наши объемы расчетные, по габаритам из справочной таблицы, а не замеры. Строка «Один усиленный двадцатифутовый» выше — тот же контейнер с нашим расчетным объемом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Выводы</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="32" customHeight="1">
-      <c r="A60" s="18" t="inlineStr">
+    <row r="82" ht="32" customHeight="1">
+      <c r="A82" s="19" t="inlineStr">
         <is>
           <t>— Усиленный двадцатифутовый паспортно берет 27 т, но до них не догружается: внутри те же 33 куб. м. Даже если грузить самое плотное вперед, в него входит 25.21 т груза плюс 618 кг доски — 25.82 т брутто, и объем кончается. Паспортной грузоподъемности не хватает 1.18 т до предела.</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="32" customHeight="1">
-      <c r="A61" s="18" t="inlineStr">
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="19" t="inlineStr">
         <is>
           <t>— В нашей очередности, с крупными клинкетами первыми, в усиленный входит еще меньше — 21.08 т. Клинкеты самые объемные на тонну: 530 кг в кубометре против 967 у средней арматуры. Чем раньше они грузятся, тем меньше тонн в корпус.</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="32" customHeight="1">
-      <c r="A62" s="18" t="inlineStr">
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="19" t="inlineStr">
         <is>
           <t>— Доска не бесплатная ни по весу, ни по месту: 618 кг и 0.88 куб. м в усиленном. Это те же полтонны неувезенной арматуры, и считать ее надо от фактического веса, а не от паспортного.</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="32" customHeight="1">
-      <c r="A63" s="18" t="inlineStr">
-        <is>
-          <t>— По деньгам в нашей очередности дешевле всего «Два двадцатифутовых по 22 т»: 632 000 руб против 926 561 у худшего варианта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="18" t="inlineStr">
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="19" t="inlineStr">
+        <is>
+          <t>— По деньгам в нашей очередности дешевле всего «Усиленный двадцатифутовый  27 т по весу»: 499 770 руб против 926 561 у худшего варианта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="32" customHeight="1">
+      <c r="A86" s="19" t="inlineStr">
         <is>
           <t>— Два обычных двадцатифутовых увозят 27.30 т и не оставляют ничего. Сорокафутовый — 25.37 т  остаток 1.92 т через транспортную компанию стоит 155 882 руб плюс отдельный день погрузки.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="18" t="inlineStr">
+    <row r="87" ht="32" customHeight="1">
+      <c r="A87" s="19" t="inlineStr">
         <is>
           <t>— Сорокафутовый при этом загружен по объему примерно наполовину: у него упор в вес, а не в место. У любого двадцатифутового наоборот.</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="18" t="inlineStr">
+    <row r="88" ht="32" customHeight="1">
+      <c r="A88" s="19" t="inlineStr">
+        <is>
+          <t>— Усиленный двадцатифутовый по паспортным 27 тоннам забирает 26.35 т груза плюс 646 кг доски — ровно 27 т брутто. Расходы: 369 000 руб контейнер с авто на обоих концах плюс 32 000 руб погрузка  итого 401 000 руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="32" customHeight="1">
+      <c r="A89" s="19" t="inlineStr">
+        <is>
+          <t>— Остаются при этом 948 кг, и это ровно те 5 позиций, у которых нет согласованной цены: задвижки желтые около крышек, блины к клинкету Ду100, коробка 2-х клапановая Ду80, электромагнитный клапан б/у и клапан Рр18-2. По договору товар без цены не считается проданным, везти его и не надо — значит, расходов по транспортной компании в этом варианте нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="32" customHeight="1">
+      <c r="A90" s="19" t="inlineStr">
         <is>
           <t>— Выгрузка в Петербурге в расчет не входит: ставок на тамошний погрузчик и грузчиков нет. По владивостокским это около 32 000 руб на контейнер.</t>
         </is>

--- a/outputs/marine_equipment/Логистика_варианты.xlsx
+++ b/outputs/marine_equipment/Логистика_варианты.xlsx
@@ -535,7 +535,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Весь перечень — 27.30 т и 38.7 куб. м, это 706 кг на кубометр. Расходы считаем полностью: контейнер, авто на обоих концах, погрузка, доска и остаток через транспортную компанию.</t>
+          <t>Весь перечень — 27.30 т и 38.3 куб. м, это 712 кг на кубометр. Расходы считаем полностью: контейнер, авто на обоих концах, погрузка, доска и остаток через транспортную компанию.</t>
         </is>
       </c>
     </row>
@@ -812,13 +812,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>26.35080994327219</v>
+        <v>26.32021577574019</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>26.99640478688236</v>
+        <v>26.96506106224583</v>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.9477732363176621</v>
+        <v>0.975</v>
       </c>
       <c r="H23" s="11" t="n">
         <v>369000</v>
@@ -835,16 +835,16 @@
         <v>32000</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>76769.63214173063</v>
+        <v>78975</v>
       </c>
       <c r="K23" s="11" t="n">
         <v>22000</v>
       </c>
       <c r="L23" s="11" t="n">
-        <v>499769.6321417306</v>
+        <v>501975</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>15217.74855737905</v>
+        <v>15235.43740737904</v>
       </c>
     </row>
     <row r="24">
@@ -857,13 +857,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>27.29858317958985</v>
+        <v>27.2952157757402</v>
       </c>
       <c r="D24" s="14" t="n">
         <v>669</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>27.9673984674898</v>
+        <v>27.96394856224583</v>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>790000</v>
       </c>
       <c r="M24" s="14" t="n">
-        <v>28939.2308312416</v>
+        <v>28942.80105681182</v>
       </c>
     </row>
     <row r="25">
@@ -900,13 +900,13 @@
         <v>2</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>27.29858317958968</v>
+        <v>27.29521577574004</v>
       </c>
       <c r="D25" s="14" t="n">
         <v>669</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>27.96739846748962</v>
+        <v>27.96394856224567</v>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>632000</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>23151.38466499343</v>
+        <v>23154.24084544959</v>
       </c>
     </row>
     <row r="26">
@@ -943,13 +943,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>21.0817771442884</v>
+        <v>21.26868631008977</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>21.59828068432347</v>
+        <v>21.78976912468697</v>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="G26" s="13" t="n">
-        <v>6.216806035301273</v>
+        <v>6.026529465650279</v>
       </c>
       <c r="H26" s="14" t="n">
         <v>369000</v>
@@ -966,16 +966,16 @@
         <v>32000</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>503561.2888594032</v>
+        <v>488148.8867176726</v>
       </c>
       <c r="K26" s="14" t="n">
         <v>22000</v>
       </c>
       <c r="L26" s="15" t="n">
-        <v>926561.2888594032</v>
+        <v>911148.8867176727</v>
       </c>
       <c r="M26" s="14" t="n">
-        <v>19021.16682362527</v>
+        <v>18854.00885384103</v>
       </c>
     </row>
     <row r="27">
@@ -988,13 +988,13 @@
         <v>1</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>25.3741099432722</v>
+        <v>25.3754157757402</v>
       </c>
       <c r="D27" s="14" t="n">
         <v>622</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>25.99577563688237</v>
+        <v>25.99711346224584</v>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="G27" s="13" t="n">
-        <v>1.924473236317662</v>
+        <v>1.9198</v>
       </c>
       <c r="H27" s="14" t="n">
         <v>509000</v>
@@ -1011,16 +1011,16 @@
         <v>32000</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>155882.3321417306</v>
+        <v>155503.8</v>
       </c>
       <c r="K27" s="14" t="n">
         <v>22000</v>
       </c>
       <c r="L27" s="15" t="n">
-        <v>718882.3321417306</v>
+        <v>718503.8</v>
       </c>
       <c r="M27" s="14" t="n">
-        <v>21320.94490051041</v>
+        <v>21319.8477132822</v>
       </c>
     </row>
     <row r="28">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>21.0817771442884</v>
+        <v>21.26868631008977</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>21.59828068432347</v>
+        <v>21.78976912468697</v>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="G28" s="13" t="n">
-        <v>6.216806035301273</v>
+        <v>6.026529465650279</v>
       </c>
       <c r="H28" s="14" t="n">
         <v>290000</v>
@@ -1056,16 +1056,16 @@
         <v>32000</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>503561.2888594032</v>
+        <v>488148.8867176726</v>
       </c>
       <c r="K28" s="14" t="n">
         <v>22000</v>
       </c>
       <c r="L28" s="15" t="n">
-        <v>847561.2888594032</v>
+        <v>832148.8867176727</v>
       </c>
       <c r="M28" s="14" t="n">
-        <v>15273.8546563774</v>
+        <v>15139.62805719903</v>
       </c>
     </row>
     <row r="29">
@@ -1078,13 +1078,13 @@
         <v>2</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>27.29858317958968</v>
+        <v>27.29521577574004</v>
       </c>
       <c r="D29" s="14" t="n">
         <v>669</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>27.96739846748962</v>
+        <v>27.96394856224567</v>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>723000</v>
       </c>
       <c r="M29" s="14" t="n">
-        <v>26484.89100125039</v>
+        <v>26488.15843553805</v>
       </c>
     </row>
     <row r="30">
@@ -1121,13 +1121,13 @@
         <v>2</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>27.29858317958986</v>
+        <v>27.29521577574021</v>
       </c>
       <c r="D30" s="14" t="n">
         <v>669</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>27.96739846748982</v>
+        <v>27.96394856224584</v>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>863000</v>
       </c>
       <c r="M30" s="14" t="n">
-        <v>31613.36228779936</v>
+        <v>31617.26242028936</v>
       </c>
     </row>
     <row r="32">
@@ -1245,13 +1245,13 @@
         <v>1</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>26.3541957647492</v>
+        <v>26.35399540838026</v>
       </c>
       <c r="D36" s="11" t="n">
         <v>646</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>26.99987356098555</v>
+        <v>26.99966829588557</v>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="G36" s="10" t="n">
-        <v>0.9443874148394101</v>
+        <v>0.9412203673587549</v>
       </c>
       <c r="H36" s="11" t="n">
         <v>369000</v>
@@ -1268,16 +1268,16 @@
         <v>32000</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>76495.38060199222</v>
+        <v>76238.84975605915</v>
       </c>
       <c r="K36" s="11" t="n">
         <v>22000</v>
       </c>
       <c r="L36" s="11" t="n">
-        <v>499495.3806019922</v>
+        <v>499238.8497560591</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>15215.79347666412</v>
+        <v>15215.90915480264</v>
       </c>
     </row>
     <row r="37">
@@ -1290,13 +1290,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>27.29858317958861</v>
+        <v>27.29521577573901</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>669</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>27.96739846748853</v>
+        <v>27.96394856224462</v>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>790000</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>28939.23083124292</v>
+        <v>28942.80105681307</v>
       </c>
     </row>
     <row r="38">
@@ -1333,13 +1333,13 @@
         <v>2</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>27.29858317958847</v>
+        <v>27.29521577573889</v>
       </c>
       <c r="D38" s="14" t="n">
         <v>669</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>27.96739846748839</v>
+        <v>27.96394856224449</v>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>632000</v>
       </c>
       <c r="M38" s="14" t="n">
-        <v>23151.38466499445</v>
+        <v>23154.24084545056</v>
       </c>
     </row>
     <row r="39">
@@ -1376,13 +1376,13 @@
         <v>1</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>25.20501317784694</v>
+        <v>25.39223271367172</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>25.82253600070419</v>
+        <v>26.01434241515668</v>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="G39" s="13" t="n">
-        <v>2.093570001741579</v>
+        <v>1.902983062067209</v>
       </c>
       <c r="H39" s="14" t="n">
         <v>369000</v>
@@ -1399,16 +1399,16 @@
         <v>32000</v>
       </c>
       <c r="J39" s="14" t="n">
-        <v>169579.1701410679</v>
+        <v>154141.6280274439</v>
       </c>
       <c r="K39" s="14" t="n">
         <v>22000</v>
       </c>
       <c r="L39" s="15" t="n">
-        <v>592579.1701410678</v>
+        <v>577141.6280274439</v>
       </c>
       <c r="M39" s="14" t="n">
-        <v>15909.53343965894</v>
+        <v>15792.23081805221</v>
       </c>
     </row>
     <row r="40">
@@ -1421,13 +1421,13 @@
         <v>1</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>25.37798218937958</v>
+        <v>25.3781043979116</v>
       </c>
       <c r="D40" s="14" t="n">
         <v>622</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>25.99974275301938</v>
+        <v>25.99986795566043</v>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="G40" s="13" t="n">
-        <v>1.920600990208946</v>
+        <v>1.917111377827328</v>
       </c>
       <c r="H40" s="14" t="n">
         <v>509000</v>
@@ -1444,16 +1444,16 @@
         <v>32000</v>
       </c>
       <c r="J40" s="14" t="n">
-        <v>155568.6802069246</v>
+        <v>155286.0216040136</v>
       </c>
       <c r="K40" s="14" t="n">
         <v>22000</v>
       </c>
       <c r="L40" s="15" t="n">
-        <v>718568.6802069247</v>
+        <v>718286.0216040136</v>
       </c>
       <c r="M40" s="14" t="n">
-        <v>21317.69168891619</v>
+        <v>21317.58903334481</v>
       </c>
     </row>
     <row r="41">
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>21.47385505985811</v>
+        <v>21.4737130047187</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>526</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>21.99996450882463</v>
+        <v>21.99981897333431</v>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="G41" s="13" t="n">
-        <v>5.824728119730372</v>
+        <v>5.821502771020196</v>
       </c>
       <c r="H41" s="14" t="n">
         <v>290000</v>
@@ -1489,16 +1489,16 @@
         <v>32000</v>
       </c>
       <c r="J41" s="14" t="n">
-        <v>471802.9776981601</v>
+        <v>471541.7244526359</v>
       </c>
       <c r="K41" s="14" t="n">
         <v>22000</v>
       </c>
       <c r="L41" s="15" t="n">
-        <v>815802.9776981601</v>
+        <v>815541.7244526359</v>
       </c>
       <c r="M41" s="14" t="n">
-        <v>14994.97873588273</v>
+        <v>14995.07793222545</v>
       </c>
     </row>
     <row r="42">
@@ -1511,13 +1511,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>27.29858317958852</v>
+        <v>27.29521577573894</v>
       </c>
       <c r="D42" s="14" t="n">
         <v>669</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>27.96739846748843</v>
+        <v>27.96394856224454</v>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>723000</v>
       </c>
       <c r="M42" s="14" t="n">
-        <v>26484.89100125152</v>
+        <v>26488.15843553913</v>
       </c>
     </row>
     <row r="43">
@@ -1554,13 +1554,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>27.29858317958853</v>
+        <v>27.29521577573893</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>669</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>27.96739846748845</v>
+        <v>27.96394856224454</v>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>863000</v>
       </c>
       <c r="M43" s="14" t="n">
-        <v>31613.3622878009</v>
+        <v>31617.26242029083</v>
       </c>
     </row>
     <row r="45">
@@ -1668,25 +1668,25 @@
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>26.35080994327219</v>
+        <v>26.32021577574019</v>
       </c>
       <c r="D47" s="14" t="n">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>26.99640478688236</v>
+        <v>26.96506106224583</v>
       </c>
       <c r="F47" s="16" t="n">
-        <v>0.9998668439586058</v>
+        <v>0.9987059652683641</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>37.9</v>
+        <v>37.7</v>
       </c>
       <c r="H47" s="13" t="n">
         <v>0.92</v>
       </c>
       <c r="I47" s="17" t="n">
-        <v>3.884877834801491e-08</v>
+        <v>3.863770755215134e-08</v>
       </c>
       <c r="J47" s="12" t="inlineStr">
         <is>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="K47" s="14" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L47" s="14" t="n">
-        <v>2872</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="48">
@@ -1712,25 +1712,25 @@
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>26.35080994327219</v>
+        <v>26.32021577574019</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>26.99640478688236</v>
+        <v>26.96506106224583</v>
       </c>
       <c r="F48" s="16" t="n">
-        <v>0.9998668439586058</v>
+        <v>0.9987059652683641</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>37.9</v>
+        <v>37.7</v>
       </c>
       <c r="H48" s="13" t="n">
         <v>0.92</v>
       </c>
       <c r="I48" s="17" t="n">
-        <v>3.884877834801491e-08</v>
+        <v>3.863770755215134e-08</v>
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="K48" s="14" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L48" s="14" t="n">
-        <v>2872</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="49">
@@ -1752,25 +1752,25 @@
         </is>
       </c>
       <c r="C49" s="13" t="n">
-        <v>0.9477732363176619</v>
+        <v>0.975</v>
       </c>
       <c r="D49" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>0.9709936806074445</v>
+        <v>0.9988875</v>
       </c>
       <c r="F49" s="17" t="n">
-        <v>0.03596272891138683</v>
+        <v>0.03699583333333333</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H49" s="13" t="n">
         <v>0.03</v>
       </c>
       <c r="I49" s="17" t="n">
-        <v>7.881720632711185e-10</v>
+        <v>6.49125e-10</v>
       </c>
       <c r="J49" s="12" t="inlineStr">
         <is>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="K49" s="14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L49" s="14" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50">
@@ -1796,16 +1796,16 @@
         </is>
       </c>
       <c r="C50" s="13" t="n">
-        <v>21.0817771442884</v>
+        <v>21.26868631008977</v>
       </c>
       <c r="D50" s="14" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>21.59828068432347</v>
+        <v>21.78976912468697</v>
       </c>
       <c r="F50" s="16" t="n">
-        <v>0.981740031105612</v>
+        <v>0.9904440511221347</v>
       </c>
       <c r="G50" s="14" t="n">
         <v>32.3</v>
@@ -1814,7 +1814,7 @@
         <v>0.74</v>
       </c>
       <c r="I50" s="16" t="n">
-        <v>0.9999806727288048</v>
+        <v>0.9999970915410201</v>
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="K50" s="14" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="L50" s="14" t="n">
-        <v>2573</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="51">
@@ -1836,25 +1836,25 @@
         </is>
       </c>
       <c r="C51" s="13" t="n">
-        <v>6.216806035301278</v>
+        <v>6.026529465650279</v>
       </c>
       <c r="D51" s="14" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E51" s="13" t="n">
-        <v>6.369117783166159</v>
+        <v>6.174179437558712</v>
       </c>
       <c r="F51" s="17" t="n">
-        <v>0.28950535378028</v>
+        <v>0.2806445198890323</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="H51" s="13" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="I51" s="17" t="n">
-        <v>0.2011390367041068</v>
+        <v>0.1905129857969015</v>
       </c>
       <c r="J51" s="12" t="inlineStr">
         <is>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="K51" s="14" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="L51" s="14" t="n">
-        <v>330</v>
+        <v>293</v>
       </c>
     </row>
     <row r="52">
@@ -1880,16 +1880,16 @@
         </is>
       </c>
       <c r="C52" s="13" t="n">
-        <v>21.0817771442884</v>
+        <v>21.26868631008977</v>
       </c>
       <c r="D52" s="14" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>21.59828068432347</v>
+        <v>21.78976912468697</v>
       </c>
       <c r="F52" s="17" t="n">
-        <v>0.7999363216416098</v>
+        <v>0.8070284860995173</v>
       </c>
       <c r="G52" s="14" t="n">
         <v>32.3</v>
@@ -1898,7 +1898,7 @@
         <v>0.74</v>
       </c>
       <c r="I52" s="16" t="n">
-        <v>0.9999806727288048</v>
+        <v>0.9999970915410201</v>
       </c>
       <c r="J52" s="12" t="inlineStr">
         <is>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="K52" s="14" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="L52" s="14" t="n">
-        <v>2573</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="53">
@@ -1924,25 +1924,25 @@
         </is>
       </c>
       <c r="C53" s="13" t="n">
-        <v>25.3741099432722</v>
+        <v>25.3754157757402</v>
       </c>
       <c r="D53" s="14" t="n">
         <v>622</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>25.99577563688237</v>
+        <v>25.99711346224584</v>
       </c>
       <c r="F53" s="16" t="n">
-        <v>0.9998375244954757</v>
+        <v>0.9998889793171477</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="H53" s="13" t="n">
         <v>0.89</v>
       </c>
       <c r="I53" s="17" t="n">
-        <v>0.5703957417859358</v>
+        <v>0.5674202314308234</v>
       </c>
       <c r="J53" s="12" t="inlineStr">
         <is>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="K53" s="14" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L53" s="14" t="n">
-        <v>2856</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="54">
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="C54" s="13" t="n">
-        <v>21.0817771442884</v>
+        <v>21.26868631008977</v>
       </c>
       <c r="D54" s="14" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E54" s="13" t="n">
-        <v>21.59828068432347</v>
+        <v>21.78976912468697</v>
       </c>
       <c r="F54" s="16" t="n">
-        <v>0.981740031105612</v>
+        <v>0.9904440511221347</v>
       </c>
       <c r="G54" s="14" t="n">
         <v>32.3</v>
@@ -1986,7 +1986,7 @@
         <v>0.74</v>
       </c>
       <c r="I54" s="16" t="n">
-        <v>0.9999806727288048</v>
+        <v>0.9999970915410201</v>
       </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="K54" s="14" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="L54" s="14" t="n">
-        <v>2573</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="55">
@@ -2012,16 +2012,16 @@
         </is>
       </c>
       <c r="C55" s="13" t="n">
-        <v>21.0817771442884</v>
+        <v>21.26868631008977</v>
       </c>
       <c r="D55" s="14" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E55" s="13" t="n">
-        <v>21.59828068432347</v>
+        <v>21.78976912468697</v>
       </c>
       <c r="F55" s="17" t="n">
-        <v>0.7999363216416098</v>
+        <v>0.8070284860995173</v>
       </c>
       <c r="G55" s="14" t="n">
         <v>32.3</v>
@@ -2030,7 +2030,7 @@
         <v>0.74</v>
       </c>
       <c r="I55" s="16" t="n">
-        <v>0.9999806727288048</v>
+        <v>0.9999970915410201</v>
       </c>
       <c r="J55" s="12" t="inlineStr">
         <is>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="K55" s="14" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="L55" s="14" t="n">
-        <v>2573</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="56">
@@ -2052,25 +2052,25 @@
         </is>
       </c>
       <c r="C56" s="13" t="n">
-        <v>6.216806035301278</v>
+        <v>6.026529465650279</v>
       </c>
       <c r="D56" s="14" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E56" s="13" t="n">
-        <v>6.369117783166159</v>
+        <v>6.174179437558712</v>
       </c>
       <c r="F56" s="17" t="n">
-        <v>0.28950535378028</v>
+        <v>0.2806445198890323</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="H56" s="13" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="I56" s="17" t="n">
-        <v>0.2011390367041068</v>
+        <v>0.1905129857969015</v>
       </c>
       <c r="J56" s="12" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="K56" s="14" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="L56" s="14" t="n">
-        <v>330</v>
+        <v>293</v>
       </c>
     </row>
     <row r="57">
@@ -2096,25 +2096,25 @@
         </is>
       </c>
       <c r="C57" s="13" t="n">
-        <v>25.3741099432722</v>
+        <v>25.3754157757402</v>
       </c>
       <c r="D57" s="14" t="n">
         <v>622</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>25.99577563688237</v>
+        <v>25.99711346224584</v>
       </c>
       <c r="F57" s="16" t="n">
-        <v>0.9998375244954757</v>
+        <v>0.9998889793171477</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="H57" s="13" t="n">
         <v>0.89</v>
       </c>
       <c r="I57" s="17" t="n">
-        <v>0.5703957417859358</v>
+        <v>0.5674202314308234</v>
       </c>
       <c r="J57" s="12" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="K57" s="14" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L57" s="14" t="n">
-        <v>2856</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="58">
@@ -2136,25 +2136,25 @@
         </is>
       </c>
       <c r="C58" s="13" t="n">
-        <v>1.924473236317661</v>
+        <v>1.9198</v>
       </c>
       <c r="D58" s="14" t="n">
         <v>47</v>
       </c>
       <c r="E58" s="13" t="n">
-        <v>1.971622830607444</v>
+        <v>1.9668351</v>
       </c>
       <c r="F58" s="17" t="n">
-        <v>0.08961921957306564</v>
+        <v>0.08940159545454544</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="H58" s="13" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I58" s="17" t="n">
-        <v>0.03958656252336723</v>
+        <v>0.03503615151515153</v>
       </c>
       <c r="J58" s="12" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>6</v>
       </c>
       <c r="L58" s="14" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61">
@@ -2178,7 +2178,7 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>— Усиленный двадцатифутовый, 27 т по весу: 0.92 куб. м, это 46 досок 4 м х 200 х 25 и 646 кг веса, которые занимают место груза.</t>
+          <t>— Усиленный двадцатифутовый, 27 т по весу: 0.92 куб. м, это 46 досок 4 м х 200 х 25 и 645 кг веса, которые занимают место груза.</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="B71" s="18" t="n">
-        <v>26351</v>
+        <v>26320</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="B72" s="18" t="n">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
@@ -2311,11 +2311,11 @@
         </is>
       </c>
       <c r="B73" s="18" t="n">
-        <v>948</v>
+        <v>975</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>5 позиций</t>
+          <t>2 позиций</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="B74" s="18" t="n">
-        <v>76770</v>
+        <v>78975</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="B76" s="11" t="n">
-        <v>499770</v>
+        <v>501975</v>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
     </row>
@@ -2392,35 +2392,35 @@
     <row r="82" ht="32" customHeight="1">
       <c r="A82" s="19" t="inlineStr">
         <is>
-          <t>— Усиленный двадцатифутовый паспортно берет 27 т, но до них не догружается: внутри те же 33 куб. м. Даже если грузить самое плотное вперед, в него входит 25.21 т груза плюс 618 кг доски — 25.82 т брутто, и объем кончается. Паспортной грузоподъемности не хватает 1.18 т до предела.</t>
+          <t>— Усиленный двадцатифутовый паспортно берет 27 т, но до них не догружается: внутри те же 33 куб. м. Даже если грузить самое плотное вперед, в него входит 25.39 т груза плюс 622 кг доски — 26.01 т брутто, и объем кончается. Паспортной грузоподъемности не хватает 0.99 т до предела.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="32" customHeight="1">
       <c r="A83" s="19" t="inlineStr">
         <is>
-          <t>— В нашей очередности, с крупными клинкетами первыми, в усиленный входит еще меньше — 21.08 т. Клинкеты самые объемные на тонну: 530 кг в кубометре против 967 у средней арматуры. Чем раньше они грузятся, тем меньше тонн в корпус.</t>
+          <t>— В нашей очередности, с крупными клинкетами первыми, в усиленный входит еще меньше — 21.27 т. Клинкеты самые объемные на тонну: 530 кг в кубометре против 967 у средней арматуры. Чем раньше они грузятся, тем меньше тонн в корпус.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="32" customHeight="1">
       <c r="A84" s="19" t="inlineStr">
         <is>
-          <t>— Доска не бесплатная ни по весу, ни по месту: 618 кг и 0.88 куб. м в усиленном. Это те же полтонны неувезенной арматуры, и считать ее надо от фактического веса, а не от паспортного.</t>
+          <t>— Доска не бесплатная ни по весу, ни по месту: 622 кг и 0.89 куб. м в усиленном. Это те же полтонны неувезенной арматуры, и считать ее надо от фактического веса, а не от паспортного.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="32" customHeight="1">
       <c r="A85" s="19" t="inlineStr">
         <is>
-          <t>— По деньгам в нашей очередности дешевле всего «Усиленный двадцатифутовый  27 т по весу»: 499 770 руб против 926 561 у худшего варианта.</t>
+          <t>— По деньгам в нашей очередности дешевле всего «Усиленный двадцатифутовый  27 т по весу»: 501 975 руб против 911 149 у худшего варианта.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="32" customHeight="1">
       <c r="A86" s="19" t="inlineStr">
         <is>
-          <t>— Два обычных двадцатифутовых увозят 27.30 т и не оставляют ничего. Сорокафутовый — 25.37 т  остаток 1.92 т через транспортную компанию стоит 155 882 руб плюс отдельный день погрузки.</t>
+          <t>— Два обычных двадцатифутовых увозят 27.30 т и не оставляют ничего. Сорокафутовый — 25.38 т  остаток 1.92 т через транспортную компанию стоит 155 504 руб плюс отдельный день погрузки.</t>
         </is>
       </c>
     </row>
@@ -2434,14 +2434,14 @@
     <row r="88" ht="32" customHeight="1">
       <c r="A88" s="19" t="inlineStr">
         <is>
-          <t>— Усиленный двадцатифутовый по паспортным 27 тоннам забирает 26.35 т груза плюс 646 кг доски — ровно 27 т брутто. Расходы: 369 000 руб контейнер с авто на обоих концах плюс 32 000 руб погрузка  итого 401 000 руб.</t>
+          <t>— Усиленный двадцатифутовый по паспортным 27 тоннам забирает 26.32 т груза плюс 645 кг доски — ровно 27 т брутто. Расходы: 369 000 руб контейнер с авто на обоих концах плюс 32 000 руб погрузка  итого 401 000 руб.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="32" customHeight="1">
       <c r="A89" s="19" t="inlineStr">
         <is>
-          <t>— Остаются при этом 948 кг, и это ровно те 5 позиций, у которых нет согласованной цены: задвижки желтые около крышек, блины к клинкету Ду100, коробка 2-х клапановая Ду80, электромагнитный клапан б/у и клапан Рр18-2. По договору товар без цены не считается проданным, везти его и не надо — значит, расходов по транспортной компании в этом варианте нет.</t>
+          <t>— Остаются при этом 975 кг, и это ровно те 2 позиций, у которых нет согласованной цены: задвижки желтые около крышек, блины к клинкету Ду100, коробка 2-х клапановая Ду80, электромагнитный клапан б/у и клапан Рр18-2. По договору товар без цены не считается проданным, везти его и не надо — значит, расходов по транспортной компании в этом варианте нет.</t>
         </is>
       </c>
     </row>

--- a/outputs/marine_equipment/Логистика_варианты.xlsx
+++ b/outputs/marine_equipment/Логистика_варианты.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Варианты" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Варианты" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -80,12 +80,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF3EA"/>
+        <fgColor rgb="00FDF2E3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDF2E3"/>
+        <fgColor rgb="00EAF3EA"/>
       </patternFill>
     </fill>
   </fills>
@@ -129,14 +129,14 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -535,7 +535,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Весь перечень — 27.30 т и 38.3 куб. м, это 712 кг на кубометр. Расходы считаем полностью: контейнер, авто на обоих концах, погрузка, доска и остаток через транспортную компанию.</t>
+          <t>Весь перечень — 28.99 т и 38.3 куб. м, это 756 кг на кубометр. Расходы считаем полностью: контейнер, авто на обоих концах, погрузка, доска и остаток через транспортную компанию.</t>
         </is>
       </c>
     </row>
@@ -812,13 +812,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>26.32021577574019</v>
+        <v>26.35225866666787</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>26.96506106224583</v>
+        <v>26.99788900400123</v>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.975</v>
+        <v>2.639853116178801</v>
       </c>
       <c r="H23" s="11" t="n">
         <v>369000</v>
@@ -835,323 +835,323 @@
         <v>32000</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>78975</v>
+        <v>213828.1024104829</v>
       </c>
       <c r="K23" s="11" t="n">
         <v>22000</v>
       </c>
-      <c r="L23" s="11" t="n">
-        <v>501975</v>
+      <c r="L23" s="12" t="n">
+        <v>636828.1024104829</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>15235.43740737904</v>
+        <v>15216.91195704648</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Два усиленных по 27 т</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="13" t="n">
-        <v>27.2952157757402</v>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>669</v>
-      </c>
-      <c r="E24" s="13" t="n">
-        <v>27.96394856224583</v>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="C24" s="10" t="n">
+        <v>28.99211178284667</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>710</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>29.70241852152641</v>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>вес, груз кончился</t>
         </is>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="G24" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="14" t="n">
+      <c r="H24" s="11" t="n">
         <v>738000</v>
       </c>
-      <c r="I24" s="14" t="n">
+      <c r="I24" s="11" t="n">
         <v>52000</v>
       </c>
-      <c r="J24" s="14" t="n">
+      <c r="J24" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="14" t="n"/>
-      <c r="L24" s="15" t="n">
+      <c r="K24" s="11" t="n"/>
+      <c r="L24" s="12" t="n">
         <v>790000</v>
       </c>
-      <c r="M24" s="14" t="n">
-        <v>28942.80105681182</v>
+      <c r="M24" s="11" t="n">
+        <v>27248.79118558751</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Два двадцатифутовых по 22 т</t>
         </is>
       </c>
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C25" s="13" t="n">
-        <v>27.29521577574004</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>669</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>27.96394856224567</v>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>груз кончился, объем</t>
-        </is>
-      </c>
-      <c r="G25" s="13" t="n">
+      <c r="C25" s="14" t="n">
+        <v>28.99211178284664</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>710</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>29.70241852152638</v>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>вес, груз кончился</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="14" t="n">
+      <c r="H25" s="15" t="n">
         <v>580000</v>
       </c>
-      <c r="I25" s="14" t="n">
+      <c r="I25" s="15" t="n">
         <v>52000</v>
       </c>
-      <c r="J25" s="14" t="n">
+      <c r="J25" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="K25" s="14" t="n"/>
+      <c r="K25" s="15" t="n"/>
       <c r="L25" s="15" t="n">
         <v>632000</v>
       </c>
-      <c r="M25" s="14" t="n">
-        <v>23154.24084544959</v>
+      <c r="M25" s="15" t="n">
+        <v>21799.03294847003</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Один усиленный двадцатифутовый</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="13" t="n">
-        <v>21.26868631008977</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>521</v>
-      </c>
-      <c r="E26" s="13" t="n">
-        <v>21.78976912468697</v>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="C26" s="10" t="n">
+        <v>23.05551333333451</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>565</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>23.6203734100012</v>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>объем</t>
         </is>
       </c>
-      <c r="G26" s="13" t="n">
-        <v>6.026529465650279</v>
-      </c>
-      <c r="H26" s="14" t="n">
+      <c r="G26" s="10" t="n">
+        <v>5.936598449512134</v>
+      </c>
+      <c r="H26" s="11" t="n">
         <v>369000</v>
       </c>
-      <c r="I26" s="14" t="n">
+      <c r="I26" s="11" t="n">
         <v>32000</v>
       </c>
-      <c r="J26" s="14" t="n">
-        <v>488148.8867176726</v>
-      </c>
-      <c r="K26" s="14" t="n">
+      <c r="J26" s="11" t="n">
+        <v>480864.4744104829</v>
+      </c>
+      <c r="K26" s="11" t="n">
         <v>22000</v>
       </c>
-      <c r="L26" s="15" t="n">
-        <v>911148.8867176727</v>
-      </c>
-      <c r="M26" s="14" t="n">
-        <v>18854.00885384103</v>
+      <c r="L26" s="12" t="n">
+        <v>903864.4744104829</v>
+      </c>
+      <c r="M26" s="11" t="n">
+        <v>17392.80293621654</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Один сорокафутовый</t>
         </is>
       </c>
-      <c r="B27" s="12" t="n">
+      <c r="B27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="13" t="n">
-        <v>25.3754157757402</v>
-      </c>
-      <c r="D27" s="14" t="n">
+      <c r="C27" s="10" t="n">
+        <v>25.37790333333452</v>
+      </c>
+      <c r="D27" s="11" t="n">
         <v>622</v>
       </c>
-      <c r="E27" s="13" t="n">
-        <v>25.99711346224584</v>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
+      <c r="E27" s="10" t="n">
+        <v>25.99966196500121</v>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>вес</t>
         </is>
       </c>
-      <c r="G27" s="13" t="n">
-        <v>1.9198</v>
-      </c>
-      <c r="H27" s="14" t="n">
+      <c r="G27" s="10" t="n">
+        <v>3.614208449512134</v>
+      </c>
+      <c r="H27" s="11" t="n">
         <v>509000</v>
       </c>
-      <c r="I27" s="14" t="n">
+      <c r="I27" s="11" t="n">
         <v>32000</v>
       </c>
-      <c r="J27" s="14" t="n">
-        <v>155503.8</v>
-      </c>
-      <c r="K27" s="14" t="n">
+      <c r="J27" s="11" t="n">
+        <v>292750.8844104829</v>
+      </c>
+      <c r="K27" s="11" t="n">
         <v>22000</v>
       </c>
-      <c r="L27" s="15" t="n">
-        <v>718503.8</v>
-      </c>
-      <c r="M27" s="14" t="n">
-        <v>21319.8477132822</v>
+      <c r="L27" s="12" t="n">
+        <v>855750.8844104828</v>
+      </c>
+      <c r="M27" s="11" t="n">
+        <v>21317.75792877983</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Один двадцатифутовый 22 т</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="13" t="n">
-        <v>21.26868631008977</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>521</v>
-      </c>
-      <c r="E28" s="13" t="n">
-        <v>21.78976912468697</v>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>объем</t>
-        </is>
-      </c>
-      <c r="G28" s="13" t="n">
-        <v>6.026529465650279</v>
-      </c>
-      <c r="H28" s="14" t="n">
+      <c r="C28" s="10" t="n">
+        <v>21.47387433333448</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>526</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>21.99998425450118</v>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>вес</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>7.51823744951214</v>
+      </c>
+      <c r="H28" s="11" t="n">
         <v>290000</v>
       </c>
-      <c r="I28" s="14" t="n">
+      <c r="I28" s="11" t="n">
         <v>32000</v>
       </c>
-      <c r="J28" s="14" t="n">
-        <v>488148.8867176726</v>
-      </c>
-      <c r="K28" s="14" t="n">
+      <c r="J28" s="11" t="n">
+        <v>608977.2334104833</v>
+      </c>
+      <c r="K28" s="11" t="n">
         <v>22000</v>
       </c>
-      <c r="L28" s="15" t="n">
-        <v>832148.8867176727</v>
-      </c>
-      <c r="M28" s="14" t="n">
-        <v>15139.62805719903</v>
+      <c r="L28" s="12" t="n">
+        <v>952977.2334104833</v>
+      </c>
+      <c r="M28" s="11" t="n">
+        <v>14994.96527741855</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Усиленный и обычный двадцатифутовые</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C29" s="13" t="n">
-        <v>27.29521577574004</v>
-      </c>
-      <c r="D29" s="14" t="n">
-        <v>669</v>
-      </c>
-      <c r="E29" s="13" t="n">
-        <v>27.96394856224567</v>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
+      <c r="C29" s="10" t="n">
+        <v>28.99211178284665</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>710</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>29.70241852152639</v>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>груз кончился, объем</t>
         </is>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="14" t="n">
+      <c r="H29" s="11" t="n">
         <v>659000</v>
       </c>
-      <c r="I29" s="14" t="n">
+      <c r="I29" s="11" t="n">
         <v>64000</v>
       </c>
-      <c r="J29" s="14" t="n">
+      <c r="J29" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K29" s="14" t="n"/>
-      <c r="L29" s="15" t="n">
+      <c r="K29" s="11" t="n"/>
+      <c r="L29" s="12" t="n">
         <v>723000</v>
       </c>
-      <c r="M29" s="14" t="n">
-        <v>26488.15843553805</v>
+      <c r="M29" s="11" t="n">
+        <v>24937.81775592378</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Сорокафутовый и двадцатифутовый</t>
         </is>
       </c>
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="13" t="n">
-        <v>27.29521577574021</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>669</v>
-      </c>
-      <c r="E30" s="13" t="n">
-        <v>27.96394856224584</v>
-      </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="C30" s="10" t="n">
+        <v>28.99211178284665</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>710</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>29.7024185215264</v>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>вес, груз кончился</t>
         </is>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="G30" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="14" t="n">
+      <c r="H30" s="11" t="n">
         <v>799000</v>
       </c>
-      <c r="I30" s="14" t="n">
+      <c r="I30" s="11" t="n">
         <v>64000</v>
       </c>
-      <c r="J30" s="14" t="n">
+      <c r="J30" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="14" t="n"/>
-      <c r="L30" s="15" t="n">
+      <c r="K30" s="11" t="n"/>
+      <c r="L30" s="12" t="n">
         <v>863000</v>
       </c>
-      <c r="M30" s="14" t="n">
-        <v>31617.26242028936</v>
+      <c r="M30" s="11" t="n">
+        <v>29766.71745969878</v>
       </c>
     </row>
     <row r="32">
@@ -1245,13 +1245,13 @@
         <v>1</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>26.35399540838026</v>
+        <v>26.35429178284544</v>
       </c>
       <c r="D36" s="11" t="n">
         <v>646</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>26.99966829588557</v>
+        <v>26.99997193152515</v>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="G36" s="10" t="n">
-        <v>0.9412203673587549</v>
+        <v>2.63782</v>
       </c>
       <c r="H36" s="11" t="n">
         <v>369000</v>
@@ -1268,323 +1268,323 @@
         <v>32000</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>76238.84975605915</v>
+        <v>213663.42</v>
       </c>
       <c r="K36" s="11" t="n">
         <v>22000</v>
       </c>
-      <c r="L36" s="11" t="n">
-        <v>499238.8497560591</v>
+      <c r="L36" s="12" t="n">
+        <v>636663.4199999999</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>15215.90915480264</v>
+        <v>15215.73804009483</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Два усиленных по 27 т</t>
         </is>
       </c>
-      <c r="B37" s="12" t="n">
+      <c r="B37" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="13" t="n">
-        <v>27.29521577573901</v>
-      </c>
-      <c r="D37" s="14" t="n">
-        <v>669</v>
-      </c>
-      <c r="E37" s="13" t="n">
-        <v>27.96394856224462</v>
-      </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="C37" s="10" t="n">
+        <v>28.99211178284543</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>710</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>29.70241852152514</v>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>вес, груз кончился</t>
         </is>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="G37" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="14" t="n">
+      <c r="H37" s="11" t="n">
         <v>738000</v>
       </c>
-      <c r="I37" s="14" t="n">
+      <c r="I37" s="11" t="n">
         <v>52000</v>
       </c>
-      <c r="J37" s="14" t="n">
+      <c r="J37" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K37" s="14" t="n"/>
-      <c r="L37" s="15" t="n">
+      <c r="K37" s="11" t="n"/>
+      <c r="L37" s="12" t="n">
         <v>790000</v>
       </c>
-      <c r="M37" s="14" t="n">
-        <v>28942.80105681307</v>
+      <c r="M37" s="11" t="n">
+        <v>27248.79118558867</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>Два двадцатифутовых по 22 т</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n">
+      <c r="B38" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C38" s="13" t="n">
-        <v>27.29521577573889</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>669</v>
-      </c>
-      <c r="E38" s="13" t="n">
-        <v>27.96394856224449</v>
-      </c>
-      <c r="F38" s="12" t="inlineStr">
+      <c r="C38" s="14" t="n">
+        <v>28.99211178284544</v>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>710</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>29.70241852152515</v>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
         <is>
           <t>вес, груз кончился</t>
         </is>
       </c>
-      <c r="G38" s="13" t="n">
+      <c r="G38" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="14" t="n">
+      <c r="H38" s="15" t="n">
         <v>580000</v>
       </c>
-      <c r="I38" s="14" t="n">
+      <c r="I38" s="15" t="n">
         <v>52000</v>
       </c>
-      <c r="J38" s="14" t="n">
+      <c r="J38" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="K38" s="14" t="n"/>
+      <c r="K38" s="15" t="n"/>
       <c r="L38" s="15" t="n">
         <v>632000</v>
       </c>
-      <c r="M38" s="14" t="n">
-        <v>23154.24084545056</v>
+      <c r="M38" s="15" t="n">
+        <v>21799.03294847093</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Один усиленный двадцатифутовый</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="13" t="n">
-        <v>25.39223271367172</v>
-      </c>
-      <c r="D39" s="14" t="n">
+      <c r="C39" s="10" t="n">
+        <v>26.35429178284544</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>646</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>26.99997193152515</v>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>вес</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>2.63782</v>
+      </c>
+      <c r="H39" s="11" t="n">
+        <v>369000</v>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>32000</v>
+      </c>
+      <c r="J39" s="11" t="n">
+        <v>213663.42</v>
+      </c>
+      <c r="K39" s="11" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>636663.4199999999</v>
+      </c>
+      <c r="M39" s="11" t="n">
+        <v>15215.73804009483</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Один сорокафутовый</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="10" t="n">
+        <v>25.37779178284544</v>
+      </c>
+      <c r="D40" s="11" t="n">
         <v>622</v>
       </c>
-      <c r="E39" s="13" t="n">
-        <v>26.01434241515668</v>
-      </c>
-      <c r="F39" s="12" t="inlineStr">
-        <is>
-          <t>объем</t>
-        </is>
-      </c>
-      <c r="G39" s="13" t="n">
-        <v>1.902983062067209</v>
-      </c>
-      <c r="H39" s="14" t="n">
-        <v>369000</v>
-      </c>
-      <c r="I39" s="14" t="n">
+      <c r="E40" s="10" t="n">
+        <v>25.99954768152515</v>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>вес</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>3.61432</v>
+      </c>
+      <c r="H40" s="11" t="n">
+        <v>509000</v>
+      </c>
+      <c r="I40" s="11" t="n">
         <v>32000</v>
       </c>
-      <c r="J39" s="14" t="n">
-        <v>154141.6280274439</v>
-      </c>
-      <c r="K39" s="14" t="n">
+      <c r="J40" s="11" t="n">
+        <v>292759.92</v>
+      </c>
+      <c r="K40" s="11" t="n">
         <v>22000</v>
       </c>
-      <c r="L39" s="15" t="n">
-        <v>577141.6280274439</v>
-      </c>
-      <c r="M39" s="14" t="n">
-        <v>15792.23081805221</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>Один сорокафутовый</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="n">
+      <c r="L40" s="12" t="n">
+        <v>855759.9199999999</v>
+      </c>
+      <c r="M40" s="11" t="n">
+        <v>21317.8516330053</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Один двадцатифутовый 22 т</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="13" t="n">
-        <v>25.3781043979116</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <v>622</v>
-      </c>
-      <c r="E40" s="13" t="n">
-        <v>25.99986795566043</v>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
+      <c r="C41" s="10" t="n">
+        <v>21.47329178284544</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>526</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>21.99938743152515</v>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>вес</t>
         </is>
       </c>
-      <c r="G40" s="13" t="n">
-        <v>1.917111377827328</v>
-      </c>
-      <c r="H40" s="14" t="n">
-        <v>509000</v>
-      </c>
-      <c r="I40" s="14" t="n">
+      <c r="G41" s="10" t="n">
+        <v>7.51882</v>
+      </c>
+      <c r="H41" s="11" t="n">
+        <v>290000</v>
+      </c>
+      <c r="I41" s="11" t="n">
         <v>32000</v>
       </c>
-      <c r="J40" s="14" t="n">
-        <v>155286.0216040136</v>
-      </c>
-      <c r="K40" s="14" t="n">
+      <c r="J41" s="11" t="n">
+        <v>609024.4199999999</v>
+      </c>
+      <c r="K41" s="11" t="n">
         <v>22000</v>
       </c>
-      <c r="L40" s="15" t="n">
-        <v>718286.0216040136</v>
-      </c>
-      <c r="M40" s="14" t="n">
-        <v>21317.58903334481</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>Один двадцатифутовый 22 т</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="13" t="n">
-        <v>21.4737130047187</v>
-      </c>
-      <c r="D41" s="14" t="n">
-        <v>526</v>
-      </c>
-      <c r="E41" s="13" t="n">
-        <v>21.99981897333431</v>
-      </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>вес</t>
-        </is>
-      </c>
-      <c r="G41" s="13" t="n">
-        <v>5.821502771020196</v>
-      </c>
-      <c r="H41" s="14" t="n">
-        <v>290000</v>
-      </c>
-      <c r="I41" s="14" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J41" s="14" t="n">
-        <v>471541.7244526359</v>
-      </c>
-      <c r="K41" s="14" t="n">
-        <v>22000</v>
-      </c>
-      <c r="L41" s="15" t="n">
-        <v>815541.7244526359</v>
-      </c>
-      <c r="M41" s="14" t="n">
-        <v>14995.07793222545</v>
+      <c r="L41" s="12" t="n">
+        <v>953024.4199999999</v>
+      </c>
+      <c r="M41" s="11" t="n">
+        <v>14995.37207691832</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Усиленный и обычный двадцатифутовые</t>
         </is>
       </c>
-      <c r="B42" s="12" t="n">
+      <c r="B42" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="13" t="n">
-        <v>27.29521577573894</v>
-      </c>
-      <c r="D42" s="14" t="n">
-        <v>669</v>
-      </c>
-      <c r="E42" s="13" t="n">
-        <v>27.96394856224454</v>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>груз кончился, объем</t>
-        </is>
-      </c>
-      <c r="G42" s="13" t="n">
+      <c r="C42" s="10" t="n">
+        <v>28.99211178284543</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>710</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>29.70241852152514</v>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>вес, груз кончился</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="14" t="n">
+      <c r="H42" s="11" t="n">
         <v>659000</v>
       </c>
-      <c r="I42" s="14" t="n">
+      <c r="I42" s="11" t="n">
         <v>64000</v>
       </c>
-      <c r="J42" s="14" t="n">
+      <c r="J42" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K42" s="14" t="n"/>
-      <c r="L42" s="15" t="n">
+      <c r="K42" s="11" t="n"/>
+      <c r="L42" s="12" t="n">
         <v>723000</v>
       </c>
-      <c r="M42" s="14" t="n">
-        <v>26488.15843553913</v>
+      <c r="M42" s="11" t="n">
+        <v>24937.81775592483</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>Сорокафутовый и двадцатифутовый</t>
         </is>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B43" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C43" s="13" t="n">
-        <v>27.29521577573893</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>669</v>
-      </c>
-      <c r="E43" s="13" t="n">
-        <v>27.96394856224454</v>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="C43" s="10" t="n">
+        <v>28.99211178284543</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>710</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>29.70241852152514</v>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
         <is>
           <t>вес, груз кончился</t>
         </is>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="G43" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="14" t="n">
+      <c r="H43" s="11" t="n">
         <v>799000</v>
       </c>
-      <c r="I43" s="14" t="n">
+      <c r="I43" s="11" t="n">
         <v>64000</v>
       </c>
-      <c r="J43" s="14" t="n">
+      <c r="J43" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K43" s="14" t="n"/>
-      <c r="L43" s="15" t="n">
+      <c r="K43" s="11" t="n"/>
+      <c r="L43" s="12" t="n">
         <v>863000</v>
       </c>
-      <c r="M43" s="14" t="n">
-        <v>31617.26242029083</v>
+      <c r="M43" s="11" t="n">
+        <v>29766.71745970003</v>
       </c>
     </row>
     <row r="45">
@@ -1657,515 +1657,515 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>Усиленный двадцатифутовый, 27 т по весу</t>
         </is>
       </c>
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>20 футов усиленный, 27 т по весу</t>
         </is>
       </c>
-      <c r="C47" s="13" t="n">
-        <v>26.32021577574019</v>
-      </c>
-      <c r="D47" s="14" t="n">
-        <v>645</v>
-      </c>
-      <c r="E47" s="13" t="n">
-        <v>26.96506106224583</v>
+      <c r="C47" s="10" t="n">
+        <v>26.35225866666787</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>646</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>26.99788900400123</v>
       </c>
       <c r="F47" s="16" t="n">
-        <v>0.9987059652683641</v>
-      </c>
-      <c r="G47" s="14" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="H47" s="13" t="n">
+        <v>0.9999218149630085</v>
+      </c>
+      <c r="G47" s="11" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="H47" s="10" t="n">
         <v>0.92</v>
       </c>
       <c r="I47" s="17" t="n">
-        <v>3.863770755215134e-08</v>
-      </c>
-      <c r="J47" s="12" t="inlineStr">
+        <v>3.747382905333394e-08</v>
+      </c>
+      <c r="J47" s="9" t="inlineStr">
         <is>
           <t>вес</t>
         </is>
       </c>
-      <c r="K47" s="14" t="n">
-        <v>285</v>
-      </c>
-      <c r="L47" s="14" t="n">
-        <v>2879</v>
+      <c r="K47" s="11" t="n">
+        <v>276</v>
+      </c>
+      <c r="L47" s="11" t="n">
+        <v>2845</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>Два усиленных по 27 т</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>20 футов усиленный, 27 т по весу</t>
         </is>
       </c>
-      <c r="C48" s="13" t="n">
-        <v>26.32021577574019</v>
-      </c>
-      <c r="D48" s="14" t="n">
-        <v>645</v>
-      </c>
-      <c r="E48" s="13" t="n">
-        <v>26.96506106224583</v>
+      <c r="C48" s="10" t="n">
+        <v>26.35225866666787</v>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>646</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>26.99788900400123</v>
       </c>
       <c r="F48" s="16" t="n">
-        <v>0.9987059652683641</v>
-      </c>
-      <c r="G48" s="14" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="H48" s="13" t="n">
+        <v>0.9999218149630085</v>
+      </c>
+      <c r="G48" s="11" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="H48" s="10" t="n">
         <v>0.92</v>
       </c>
       <c r="I48" s="17" t="n">
-        <v>3.863770755215134e-08</v>
-      </c>
-      <c r="J48" s="12" t="inlineStr">
+        <v>3.747382905333394e-08</v>
+      </c>
+      <c r="J48" s="9" t="inlineStr">
         <is>
           <t>вес</t>
         </is>
       </c>
-      <c r="K48" s="14" t="n">
-        <v>285</v>
-      </c>
-      <c r="L48" s="14" t="n">
-        <v>2879</v>
+      <c r="K48" s="11" t="n">
+        <v>276</v>
+      </c>
+      <c r="L48" s="11" t="n">
+        <v>2845</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="inlineStr"/>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="A49" s="9" t="inlineStr"/>
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>20 футов усиленный, 27 т по весу</t>
         </is>
       </c>
-      <c r="C49" s="13" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="D49" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="E49" s="13" t="n">
-        <v>0.9988875</v>
+      <c r="C49" s="10" t="n">
+        <v>2.6398531161788</v>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>2.704529517525181</v>
       </c>
       <c r="F49" s="17" t="n">
-        <v>0.03699583333333333</v>
-      </c>
-      <c r="G49" s="14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H49" s="13" t="n">
-        <v>0.03</v>
+        <v>0.1001677599083401</v>
+      </c>
+      <c r="G49" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H49" s="10" t="n">
+        <v>0.09</v>
       </c>
       <c r="I49" s="17" t="n">
-        <v>6.49125e-10</v>
-      </c>
-      <c r="J49" s="12" t="inlineStr">
+        <v>1.872394859066258e-09</v>
+      </c>
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>груз кончился</t>
         </is>
       </c>
-      <c r="K49" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L49" s="14" t="n">
-        <v>23</v>
+      <c r="K49" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="L49" s="11" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>Два двадцатифутовых по 22 т</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>20 футов, 22 т</t>
         </is>
       </c>
-      <c r="C50" s="13" t="n">
-        <v>21.26868631008977</v>
-      </c>
-      <c r="D50" s="14" t="n">
-        <v>521</v>
-      </c>
-      <c r="E50" s="13" t="n">
-        <v>21.78976912468697</v>
+      <c r="C50" s="10" t="n">
+        <v>21.47387433333448</v>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>526</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>21.99998425450118</v>
       </c>
       <c r="F50" s="16" t="n">
-        <v>0.9904440511221347</v>
-      </c>
-      <c r="G50" s="14" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="H50" s="13" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I50" s="16" t="n">
-        <v>0.9999970915410201</v>
-      </c>
-      <c r="J50" s="12" t="inlineStr">
+        <v>0.9999992842955081</v>
+      </c>
+      <c r="G50" s="11" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="H50" s="10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I50" s="17" t="n">
+        <v>0.9212450182323375</v>
+      </c>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>вес</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="n">
+        <v>226</v>
+      </c>
+      <c r="L50" s="11" t="n">
+        <v>2642</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr"/>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>20 футов, 22 т</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="n">
+        <v>7.518237449512152</v>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>184</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>7.7024342670252</v>
+      </c>
+      <c r="F51" s="17" t="n">
+        <v>0.3501106485011454</v>
+      </c>
+      <c r="G51" s="11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H51" s="10" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I51" s="17" t="n">
+        <v>0.2710647972949372</v>
+      </c>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>груз кончился</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="L51" s="11" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Один усиленный двадцатифутовый</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>20 футов усиленный, 27 т</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="n">
+        <v>23.05551333333451</v>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>565</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>23.6203734100012</v>
+      </c>
+      <c r="F52" s="17" t="n">
+        <v>0.8748286448148594</v>
+      </c>
+      <c r="G52" s="11" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="H52" s="10" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I52" s="16" t="n">
+        <v>0.9999831202020356</v>
+      </c>
+      <c r="J52" s="9" t="inlineStr">
         <is>
           <t>объем</t>
         </is>
       </c>
-      <c r="K50" s="14" t="n">
-        <v>221</v>
-      </c>
-      <c r="L50" s="14" t="n">
-        <v>2609</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="12" t="inlineStr"/>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="K52" s="11" t="n">
+        <v>237</v>
+      </c>
+      <c r="L52" s="11" t="n">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>Один сорокафутовый</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>40 футов, 26 т</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="n">
+        <v>25.37790333333452</v>
+      </c>
+      <c r="D53" s="11" t="n">
+        <v>622</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>25.99966196500121</v>
+      </c>
+      <c r="F53" s="16" t="n">
+        <v>0.9999869986538927</v>
+      </c>
+      <c r="G53" s="11" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="H53" s="10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I53" s="17" t="n">
+        <v>0.5385971222718343</v>
+      </c>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>вес</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="n">
+        <v>247</v>
+      </c>
+      <c r="L53" s="11" t="n">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Один двадцатифутовый 22 т</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>20 футов, 22 т</t>
         </is>
       </c>
-      <c r="C51" s="13" t="n">
-        <v>6.026529465650279</v>
-      </c>
-      <c r="D51" s="14" t="n">
-        <v>148</v>
-      </c>
-      <c r="E51" s="13" t="n">
-        <v>6.174179437558712</v>
-      </c>
-      <c r="F51" s="17" t="n">
-        <v>0.2806445198890323</v>
-      </c>
-      <c r="G51" s="14" t="n">
+      <c r="C54" s="10" t="n">
+        <v>21.47387433333448</v>
+      </c>
+      <c r="D54" s="11" t="n">
+        <v>526</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>21.99998425450118</v>
+      </c>
+      <c r="F54" s="16" t="n">
+        <v>0.9999992842955081</v>
+      </c>
+      <c r="G54" s="11" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="H54" s="10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I54" s="17" t="n">
+        <v>0.9212450182323375</v>
+      </c>
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t>вес</t>
+        </is>
+      </c>
+      <c r="K54" s="11" t="n">
+        <v>226</v>
+      </c>
+      <c r="L54" s="11" t="n">
+        <v>2642</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>Усиленный и обычный двадцатифутовые</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>20 футов усиленный, 27 т</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="n">
+        <v>23.05551333333451</v>
+      </c>
+      <c r="D55" s="11" t="n">
+        <v>565</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>23.6203734100012</v>
+      </c>
+      <c r="F55" s="17" t="n">
+        <v>0.8748286448148594</v>
+      </c>
+      <c r="G55" s="11" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="H55" s="10" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I55" s="16" t="n">
+        <v>0.9999831202020356</v>
+      </c>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>объем</t>
+        </is>
+      </c>
+      <c r="K55" s="11" t="n">
+        <v>237</v>
+      </c>
+      <c r="L55" s="11" t="n">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr"/>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>20 футов, 22 т</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="n">
+        <v>5.936598449512138</v>
+      </c>
+      <c r="D56" s="11" t="n">
+        <v>145</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>6.082045111525185</v>
+      </c>
+      <c r="F56" s="17" t="n">
+        <v>0.2764565959784175</v>
+      </c>
+      <c r="G56" s="11" t="n">
         <v>6.1</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="H56" s="10" t="n">
         <v>0.21</v>
       </c>
-      <c r="I51" s="17" t="n">
-        <v>0.1905129857969015</v>
-      </c>
-      <c r="J51" s="12" t="inlineStr">
+      <c r="I56" s="17" t="n">
+        <v>0.1923266953252396</v>
+      </c>
+      <c r="J56" s="9" t="inlineStr">
         <is>
           <t>груз кончился</t>
         </is>
       </c>
-      <c r="K51" s="14" t="n">
-        <v>67</v>
-      </c>
-      <c r="L51" s="14" t="n">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t>Один усиленный двадцатифутовый</t>
-        </is>
-      </c>
-      <c r="B52" s="12" t="inlineStr">
-        <is>
-          <t>20 футов усиленный, 27 т</t>
-        </is>
-      </c>
-      <c r="C52" s="13" t="n">
-        <v>21.26868631008977</v>
-      </c>
-      <c r="D52" s="14" t="n">
-        <v>521</v>
-      </c>
-      <c r="E52" s="13" t="n">
-        <v>21.78976912468697</v>
-      </c>
-      <c r="F52" s="17" t="n">
-        <v>0.8070284860995173</v>
-      </c>
-      <c r="G52" s="14" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="H52" s="13" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I52" s="16" t="n">
-        <v>0.9999970915410201</v>
-      </c>
-      <c r="J52" s="12" t="inlineStr">
-        <is>
-          <t>объем</t>
-        </is>
-      </c>
-      <c r="K52" s="14" t="n">
-        <v>221</v>
-      </c>
-      <c r="L52" s="14" t="n">
-        <v>2609</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="12" t="inlineStr">
-        <is>
-          <t>Один сорокафутовый</t>
-        </is>
-      </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="K56" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="L56" s="11" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Сорокафутовый и двадцатифутовый</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>40 футов, 26 т</t>
         </is>
       </c>
-      <c r="C53" s="13" t="n">
-        <v>25.3754157757402</v>
-      </c>
-      <c r="D53" s="14" t="n">
+      <c r="C57" s="10" t="n">
+        <v>25.37790333333452</v>
+      </c>
+      <c r="D57" s="11" t="n">
         <v>622</v>
       </c>
-      <c r="E53" s="13" t="n">
-        <v>25.99711346224584</v>
-      </c>
-      <c r="F53" s="16" t="n">
-        <v>0.9998889793171477</v>
-      </c>
-      <c r="G53" s="14" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="H53" s="13" t="n">
+      <c r="E57" s="10" t="n">
+        <v>25.99966196500121</v>
+      </c>
+      <c r="F57" s="16" t="n">
+        <v>0.9999869986538927</v>
+      </c>
+      <c r="G57" s="11" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="H57" s="10" t="n">
         <v>0.89</v>
       </c>
-      <c r="I53" s="17" t="n">
-        <v>0.5674202314308234</v>
-      </c>
-      <c r="J53" s="12" t="inlineStr">
+      <c r="I57" s="17" t="n">
+        <v>0.5385971222718343</v>
+      </c>
+      <c r="J57" s="9" t="inlineStr">
         <is>
           <t>вес</t>
         </is>
       </c>
-      <c r="K53" s="14" t="n">
-        <v>282</v>
-      </c>
-      <c r="L53" s="14" t="n">
-        <v>2860</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>Один двадцатифутовый 22 т</t>
-        </is>
-      </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="K57" s="11" t="n">
+        <v>247</v>
+      </c>
+      <c r="L57" s="11" t="n">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr"/>
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>20 футов, 22 т</t>
         </is>
       </c>
-      <c r="C54" s="13" t="n">
-        <v>21.26868631008977</v>
-      </c>
-      <c r="D54" s="14" t="n">
-        <v>521</v>
-      </c>
-      <c r="E54" s="13" t="n">
-        <v>21.78976912468697</v>
-      </c>
-      <c r="F54" s="16" t="n">
-        <v>0.9904440511221347</v>
-      </c>
-      <c r="G54" s="14" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="H54" s="13" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I54" s="16" t="n">
-        <v>0.9999970915410201</v>
-      </c>
-      <c r="J54" s="12" t="inlineStr">
-        <is>
-          <t>объем</t>
-        </is>
-      </c>
-      <c r="K54" s="14" t="n">
-        <v>221</v>
-      </c>
-      <c r="L54" s="14" t="n">
-        <v>2609</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="12" t="inlineStr">
-        <is>
-          <t>Усиленный и обычный двадцатифутовые</t>
-        </is>
-      </c>
-      <c r="B55" s="12" t="inlineStr">
-        <is>
-          <t>20 футов усиленный, 27 т</t>
-        </is>
-      </c>
-      <c r="C55" s="13" t="n">
-        <v>21.26868631008977</v>
-      </c>
-      <c r="D55" s="14" t="n">
-        <v>521</v>
-      </c>
-      <c r="E55" s="13" t="n">
-        <v>21.78976912468697</v>
-      </c>
-      <c r="F55" s="17" t="n">
-        <v>0.8070284860995173</v>
-      </c>
-      <c r="G55" s="14" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="H55" s="13" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I55" s="16" t="n">
-        <v>0.9999970915410201</v>
-      </c>
-      <c r="J55" s="12" t="inlineStr">
-        <is>
-          <t>объем</t>
-        </is>
-      </c>
-      <c r="K55" s="14" t="n">
-        <v>221</v>
-      </c>
-      <c r="L55" s="14" t="n">
-        <v>2609</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="12" t="inlineStr"/>
-      <c r="B56" s="12" t="inlineStr">
-        <is>
-          <t>20 футов, 22 т</t>
-        </is>
-      </c>
-      <c r="C56" s="13" t="n">
-        <v>6.026529465650279</v>
-      </c>
-      <c r="D56" s="14" t="n">
-        <v>148</v>
-      </c>
-      <c r="E56" s="13" t="n">
-        <v>6.174179437558712</v>
-      </c>
-      <c r="F56" s="17" t="n">
-        <v>0.2806445198890323</v>
-      </c>
-      <c r="G56" s="14" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="H56" s="13" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I56" s="17" t="n">
-        <v>0.1905129857969015</v>
-      </c>
-      <c r="J56" s="12" t="inlineStr">
+      <c r="C58" s="10" t="n">
+        <v>3.614208449512136</v>
+      </c>
+      <c r="D58" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>3.702756556525184</v>
+      </c>
+      <c r="F58" s="17" t="n">
+        <v>0.1683071162056902</v>
+      </c>
+      <c r="G58" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H58" s="10" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I58" s="17" t="n">
+        <v>0.09553022108281571</v>
+      </c>
+      <c r="J58" s="9" t="inlineStr">
         <is>
           <t>груз кончился</t>
         </is>
       </c>
-      <c r="K56" s="14" t="n">
-        <v>67</v>
-      </c>
-      <c r="L56" s="14" t="n">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>Сорокафутовый и двадцатифутовый</t>
-        </is>
-      </c>
-      <c r="B57" s="12" t="inlineStr">
-        <is>
-          <t>40 футов, 26 т</t>
-        </is>
-      </c>
-      <c r="C57" s="13" t="n">
-        <v>25.3754157757402</v>
-      </c>
-      <c r="D57" s="14" t="n">
-        <v>622</v>
-      </c>
-      <c r="E57" s="13" t="n">
-        <v>25.99711346224584</v>
-      </c>
-      <c r="F57" s="16" t="n">
-        <v>0.9998889793171477</v>
-      </c>
-      <c r="G57" s="14" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="H57" s="13" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I57" s="17" t="n">
-        <v>0.5674202314308234</v>
-      </c>
-      <c r="J57" s="12" t="inlineStr">
-        <is>
-          <t>вес</t>
-        </is>
-      </c>
-      <c r="K57" s="14" t="n">
-        <v>282</v>
-      </c>
-      <c r="L57" s="14" t="n">
-        <v>2860</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="inlineStr"/>
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>20 футов, 22 т</t>
-        </is>
-      </c>
-      <c r="C58" s="13" t="n">
-        <v>1.9198</v>
-      </c>
-      <c r="D58" s="14" t="n">
-        <v>47</v>
-      </c>
-      <c r="E58" s="13" t="n">
-        <v>1.9668351</v>
-      </c>
-      <c r="F58" s="17" t="n">
-        <v>0.08940159545454544</v>
-      </c>
-      <c r="G58" s="14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H58" s="13" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I58" s="17" t="n">
-        <v>0.03503615151515153</v>
-      </c>
-      <c r="J58" s="12" t="inlineStr">
-        <is>
-          <t>груз кончился</t>
-        </is>
-      </c>
-      <c r="K58" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="L58" s="14" t="n">
+      <c r="K58" s="11" t="n">
         <v>42</v>
+      </c>
+      <c r="L58" s="11" t="n">
+        <v>121</v>
       </c>
     </row>
     <row r="61">
@@ -2178,21 +2178,21 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>— Усиленный двадцатифутовый, 27 т по весу: 0.92 куб. м, это 46 досок 4 м х 200 х 25 и 645 кг веса, которые занимают место груза.</t>
+          <t>— Усиленный двадцатифутовый, 27 т по весу: 0.92 куб. м, это 46 досок 4 м х 200 х 25 и 646 кг веса, которые занимают место груза.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>— Два усиленных по 27 т: 0.96 куб. м, это 48 досок 4 м х 200 х 25 и 669 кг веса, которые занимают место груза.</t>
+          <t>— Два усиленных по 27 т: 1.01 куб. м, это 51 досок 4 м х 200 х 25 и 710 кг веса, которые занимают место груза.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>— Два двадцатифутовых по 22 т: 0.96 куб. м, это 48 досок 4 м х 200 х 25 и 669 кг веса, которые занимают место груза.</t>
+          <t>— Два двадцатифутовых по 22 т: 1.01 куб. м, это 51 досок 4 м х 200 х 25 и 710 кг веса, которые занимают место груза.</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="B71" s="18" t="n">
-        <v>26320</v>
+        <v>26352</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="B72" s="18" t="n">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
@@ -2311,11 +2311,11 @@
         </is>
       </c>
       <c r="B73" s="18" t="n">
-        <v>975</v>
+        <v>2640</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>2 позиций</t>
+          <t>11 позиций</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="B74" s="18" t="n">
-        <v>78975</v>
+        <v>213828</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
@@ -2355,8 +2355,8 @@
           <t>ВСЕГО с остатком через ТК</t>
         </is>
       </c>
-      <c r="B76" s="11" t="n">
-        <v>501975</v>
+      <c r="B76" s="15" t="n">
+        <v>636828</v>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
     </row>
@@ -2366,7 +2366,7 @@
           <t>ВСЕГО без остатка</t>
         </is>
       </c>
-      <c r="B77" s="11" t="n">
+      <c r="B77" s="15" t="n">
         <v>401000</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -2392,35 +2392,35 @@
     <row r="82" ht="32" customHeight="1">
       <c r="A82" s="19" t="inlineStr">
         <is>
-          <t>— Усиленный двадцатифутовый паспортно берет 27 т, но до них не догружается: внутри те же 33 куб. м. Даже если грузить самое плотное вперед, в него входит 25.39 т груза плюс 622 кг доски — 26.01 т брутто, и объем кончается. Паспортной грузоподъемности не хватает 0.99 т до предела.</t>
+          <t>— Усиленный двадцатифутовый паспортно берет 27 т, но до них не догружается: внутри те же 33 куб. м. Даже если грузить самое плотное вперед, в него входит 26.35 т груза плюс 646 кг доски — 27.00 т брутто, и объем кончается. Паспортной грузоподъемности не хватает 0.00 т до предела.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="32" customHeight="1">
       <c r="A83" s="19" t="inlineStr">
         <is>
-          <t>— В нашей очередности, с крупными клинкетами первыми, в усиленный входит еще меньше — 21.27 т. Клинкеты самые объемные на тонну: 530 кг в кубометре против 967 у средней арматуры. Чем раньше они грузятся, тем меньше тонн в корпус.</t>
+          <t>— В нашей очередности, с крупными клинкетами первыми, в усиленный входит еще меньше — 23.06 т. Клинкеты самые объемные на тонну: 530 кг в кубометре против 967 у средней арматуры. Чем раньше они грузятся, тем меньше тонн в корпус.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="32" customHeight="1">
       <c r="A84" s="19" t="inlineStr">
         <is>
-          <t>— Доска не бесплатная ни по весу, ни по месту: 622 кг и 0.89 куб. м в усиленном. Это те же полтонны неувезенной арматуры, и считать ее надо от фактического веса, а не от паспортного.</t>
+          <t>— Доска не бесплатная ни по весу, ни по месту: 646 кг и 0.92 куб. м в усиленном. Это те же полтонны неувезенной арматуры, и считать ее надо от фактического веса, а не от паспортного.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="32" customHeight="1">
       <c r="A85" s="19" t="inlineStr">
         <is>
-          <t>— По деньгам в нашей очередности дешевле всего «Усиленный двадцатифутовый  27 т по весу»: 501 975 руб против 911 149 у худшего варианта.</t>
+          <t>— По деньгам в нашей очередности дешевле всего «Два двадцатифутовых по 22 т»: 632 000 руб против 952 977 у худшего варианта.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="32" customHeight="1">
       <c r="A86" s="19" t="inlineStr">
         <is>
-          <t>— Два обычных двадцатифутовых увозят 27.30 т и не оставляют ничего. Сорокафутовый — 25.38 т  остаток 1.92 т через транспортную компанию стоит 155 504 руб плюс отдельный день погрузки.</t>
+          <t>— Два обычных двадцатифутовых увозят 28.99 т и не оставляют ничего. Сорокафутовый — 25.38 т  остаток 3.61 т через транспортную компанию стоит 292 751 руб плюс отдельный день погрузки.</t>
         </is>
       </c>
     </row>
@@ -2434,14 +2434,14 @@
     <row r="88" ht="32" customHeight="1">
       <c r="A88" s="19" t="inlineStr">
         <is>
-          <t>— Усиленный двадцатифутовый по паспортным 27 тоннам забирает 26.32 т груза плюс 645 кг доски — ровно 27 т брутто. Расходы: 369 000 руб контейнер с авто на обоих концах плюс 32 000 руб погрузка  итого 401 000 руб.</t>
+          <t>— Усиленный двадцатифутовый по паспортным 27 тоннам забирает 26.35 т груза плюс 646 кг доски — ровно 27 т брутто. Расходы: 369 000 руб контейнер с авто на обоих концах плюс 32 000 руб погрузка  итого 401 000 руб.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="32" customHeight="1">
       <c r="A89" s="19" t="inlineStr">
         <is>
-          <t>— Остаются при этом 975 кг, и это ровно те 2 позиций, у которых нет согласованной цены: задвижки желтые около крышек, блины к клинкету Ду100, коробка 2-х клапановая Ду80, электромагнитный клапан б/у и клапан Рр18-2. По договору товар без цены не считается проданным, везти его и не надо — значит, расходов по транспортной компании в этом варианте нет.</t>
+          <t>— Остаются при этом 2640 кг, и это ровно те 11 позиций, у которых нет согласованной цены: задвижки желтые около крышек, блины к клинкету Ду100, коробка 2-х клапановая Ду80, электромагнитный клапан б/у и клапан Рр18-2. По договору товар без цены не считается проданным, везти его и не надо — значит, расходов по транспортной компании в этом варианте нет.</t>
         </is>
       </c>
     </row>
